--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_11_43.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_11_43.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5029085.337810092</v>
+        <v>4988483.110494855</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6763050.571139444</v>
+        <v>6770031.521537242</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6763050.571139444</v>
+        <v>6770031.521537242</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3006462.165424415</v>
+        <v>3017918.176595663</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3006462.165424415</v>
+        <v>3017918.176595663</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>44107751.29892301</v>
+        <v>44110863.56417618</v>
       </c>
     </row>
   </sheetData>
@@ -666,10 +666,10 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F2" t="n">
-        <v>4.889628708011855</v>
+        <v>404.8896287080119</v>
       </c>
       <c r="G2" t="n">
-        <v>403.7573722870162</v>
+        <v>3.75737228701621</v>
       </c>
       <c r="H2" t="n">
         <v>408.0096587035274</v>
@@ -678,28 +678,28 @@
         <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
-        <v>419.7382696589336</v>
+        <v>418.7382696589336</v>
       </c>
       <c r="K2" t="n">
-        <v>98.12488247690067</v>
+        <v>507.7400371911698</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M2" t="n">
-        <v>676.2121520328244</v>
+        <v>297.9910820919849</v>
       </c>
       <c r="N2" t="n">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="O2" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>371.9706110579117</v>
+        <v>370.9706110579117</v>
       </c>
       <c r="R2" t="n">
         <v>250.8785988282945</v>
@@ -708,7 +708,7 @@
         <v>494.8481678023229</v>
       </c>
       <c r="T2" t="n">
-        <v>283.1660146029995</v>
+        <v>279.285214602999</v>
       </c>
       <c r="U2" t="n">
         <v>249.2212965486107</v>
@@ -736,19 +736,19 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>156.9894696000266</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
         <v>66.5639999646113</v>
       </c>
       <c r="T3" t="n">
-        <v>5.357765217513816</v>
+        <v>194.6717565039966</v>
       </c>
       <c r="U3" t="n">
         <v>0.2103597601867477</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>23.54762815777917</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>120.6316114025499</v>
@@ -860,7 +860,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>326.6021279811511</v>
+        <v>320.9396782847086</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -906,34 +906,34 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>100.2478051614515</v>
+        <v>403.7573722870162</v>
       </c>
       <c r="H5" t="n">
-        <v>408.0096587035274</v>
+        <v>104.5000915779626</v>
       </c>
       <c r="I5" t="n">
         <v>150.0811596826846</v>
       </c>
       <c r="J5" t="n">
-        <v>798.7814999999999</v>
+        <v>419.7382696589336</v>
       </c>
       <c r="K5" t="n">
-        <v>395.2938041686553</v>
+        <v>66.13418277954936</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="M5" t="n">
+        <v>512.6173161491834</v>
+      </c>
+      <c r="N5" t="n">
+        <v>195.5855355810472</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>815</v>
-      </c>
-      <c r="N5" t="n">
-        <v>815</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>371.9706110579117</v>
@@ -945,10 +945,10 @@
         <v>494.8481678023229</v>
       </c>
       <c r="T5" t="n">
-        <v>586.6755817285639</v>
+        <v>186.6755817285639</v>
       </c>
       <c r="U5" t="n">
-        <v>249.2212965486107</v>
+        <v>649.2212965486107</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -970,28 +970,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>73.16906773709609</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>314.8597026170468</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1027,7 +1027,7 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U6" t="n">
-        <v>400.2103597601867</v>
+        <v>0.2103597601867477</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
@@ -1131,10 +1131,10 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C8" t="n">
-        <v>449.4745782429939</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D8" t="n">
-        <v>410.3391557398498</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E8" t="n">
         <v>4.363289606868648</v>
@@ -1143,10 +1143,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.75737228701621</v>
+        <v>351.1264039897458</v>
       </c>
       <c r="H8" t="n">
-        <v>355.3786904062572</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
         <v>150.0811596826846</v>
@@ -1155,19 +1155,19 @@
         <v>419.7382696589336</v>
       </c>
       <c r="K8" t="n">
-        <v>66.13418277959416</v>
+        <v>98.12488247690067</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>377.2210699407718</v>
       </c>
       <c r="M8" t="n">
+        <v>298.9910820919849</v>
+      </c>
+      <c r="N8" t="n">
         <v>815</v>
       </c>
-      <c r="N8" t="n">
-        <v>195.5855355810472</v>
-      </c>
       <c r="O8" t="n">
-        <v>512.6173161491826</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>815</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>494.8481678023229</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T8" t="n">
         <v>186.6755817285639</v>
@@ -1191,13 +1191,13 @@
         <v>229.8510241668239</v>
       </c>
       <c r="W8" t="n">
-        <v>238.3734759809475</v>
+        <v>638.3734759809475</v>
       </c>
       <c r="X8" t="n">
-        <v>192.2818334606677</v>
+        <v>592.2818334606677</v>
       </c>
       <c r="Y8" t="n">
-        <v>111.3174326828064</v>
+        <v>511.3174326828064</v>
       </c>
     </row>
     <row r="9">
@@ -1213,13 +1213,13 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>175.4172848236332</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>58.33423161728823</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1270,13 +1270,13 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>32.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X9" t="n">
         <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="10">
@@ -1374,16 +1374,16 @@
         <v>185.3391557398498</v>
       </c>
       <c r="E11" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1416,16 +1416,16 @@
         <v>25.87859882829446</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>212.4397096648669</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>361.6755817285639</v>
       </c>
       <c r="U11" t="n">
         <v>424.2212965486107</v>
       </c>
       <c r="V11" t="n">
-        <v>257.9463662548307</v>
+        <v>404.8510241668239</v>
       </c>
       <c r="W11" t="n">
         <v>413.3734759809475</v>
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>17.65001814420742</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>198.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1571,7 +1571,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>340.7767994885276</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>62.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1796,13 +1796,13 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>320.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>208.3954718840232</v>
+        <v>92.13264982743065</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>436.4478973282775</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
         <v>125.3632896068686</v>
       </c>
       <c r="F17" t="n">
-        <v>125.8896287080119</v>
+        <v>129.3398200934258</v>
       </c>
       <c r="G17" t="n">
         <v>124.7573722870162</v>
@@ -1860,7 +1860,7 @@
         <v>129.0096587035274</v>
       </c>
       <c r="I17" t="n">
-        <v>3.450191385413969</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>361.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>16.34743437468334</v>
+        <v>338.6387678008247</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2094,10 +2094,10 @@
         <v>124.7573722870162</v>
       </c>
       <c r="H20" t="n">
-        <v>132.4598500889414</v>
+        <v>129.0096587035274</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>3.450191385413969</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2279,10 +2279,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>446.839266425598</v>
+        <v>338.6387678008247</v>
       </c>
       <c r="R22" t="n">
-        <v>339.4016293563778</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2331,10 +2331,10 @@
         <v>124.7573722870162</v>
       </c>
       <c r="H23" t="n">
-        <v>132.4598500889414</v>
+        <v>129.0096587035274</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>3.450191385413969</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2550,10 +2550,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>256.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>224.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>185.3391557398498</v>
@@ -2562,10 +2562,10 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>24.69037970762734</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>183.0096587035274</v>
@@ -2607,7 +2607,7 @@
         <v>361.6755817285639</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>424.2212965486107</v>
       </c>
       <c r="V26" t="n">
         <v>404.8510241668239</v>
@@ -2619,7 +2619,7 @@
         <v>367.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>286.3174326828064</v>
+        <v>180.6091783323831</v>
       </c>
     </row>
     <row r="27">
@@ -2750,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>340.7767994885276</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -2787,25 +2787,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>241.9993129555745</v>
+        <v>236.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>209.4745782429939</v>
+        <v>204.4745782429939</v>
       </c>
       <c r="D29" t="n">
-        <v>170.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>164.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>164.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>52.73991437502322</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>168.0096587035274</v>
+        <v>161.0562976023941</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2835,28 +2835,28 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>10.87859882829446</v>
+        <v>5.878598828294457</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>249.8481678023229</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>341.6755817285639</v>
       </c>
       <c r="U29" t="n">
-        <v>409.2212965486107</v>
+        <v>404.2212965486107</v>
       </c>
       <c r="V29" t="n">
-        <v>389.8510241668239</v>
+        <v>384.8510241668239</v>
       </c>
       <c r="W29" t="n">
-        <v>398.3734759809475</v>
+        <v>393.3734759809475</v>
       </c>
       <c r="X29" t="n">
-        <v>352.2818334606677</v>
+        <v>347.2818334606677</v>
       </c>
       <c r="Y29" t="n">
-        <v>271.3174326828064</v>
+        <v>266.3174326828064</v>
       </c>
     </row>
     <row r="30">
@@ -2866,25 +2866,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>144.5565566463266</v>
+        <v>139.5565566463266</v>
       </c>
       <c r="C30" t="n">
-        <v>121.0999124455193</v>
+        <v>116.0999124455193</v>
       </c>
       <c r="D30" t="n">
-        <v>107.9376868977026</v>
+        <v>102.9376868977026</v>
       </c>
       <c r="E30" t="n">
-        <v>102.6720972219126</v>
+        <v>97.67209722191262</v>
       </c>
       <c r="F30" t="n">
-        <v>99.63624233787687</v>
+        <v>94.63624233787687</v>
       </c>
       <c r="G30" t="n">
-        <v>85.73953587502734</v>
+        <v>80.73953587502734</v>
       </c>
       <c r="H30" t="n">
-        <v>92.16808718642113</v>
+        <v>87.16808718642113</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2914,28 +2914,28 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>307.2737972923793</v>
+        <v>302.2737972923793</v>
       </c>
       <c r="S30" t="n">
-        <v>226.5639999646113</v>
+        <v>221.5639999646113</v>
       </c>
       <c r="T30" t="n">
-        <v>165.3577652175138</v>
+        <v>160.3577652175138</v>
       </c>
       <c r="U30" t="n">
-        <v>160.2103597601867</v>
+        <v>155.2103597601867</v>
       </c>
       <c r="V30" t="n">
-        <v>174.5106671915202</v>
+        <v>169.5106671915202</v>
       </c>
       <c r="W30" t="n">
-        <v>192.3731429098285</v>
+        <v>187.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>179.8627394453875</v>
+        <v>174.8627394453875</v>
       </c>
       <c r="Y30" t="n">
-        <v>159.3913927661343</v>
+        <v>154.3913927661343</v>
       </c>
     </row>
     <row r="31">
@@ -2954,7 +2954,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>40.98090483695654</v>
+        <v>35.98090483695654</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>178.5476281577792</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>402.8087589767836</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>263.5646308190044</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3039,7 +3039,7 @@
         <v>114.8896287080119</v>
       </c>
       <c r="G32" t="n">
-        <v>113.7573722870162</v>
+        <v>104.3331636724305</v>
       </c>
       <c r="H32" t="n">
         <v>118.0096587035274</v>
@@ -3048,19 +3048,19 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>758.5974</v>
+        <v>376.7382696589336</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>506.4308407844086</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>660.110409970511</v>
       </c>
       <c r="M32" t="n">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="N32" t="n">
-        <v>154.5855355810472</v>
+        <v>152.5855355810472</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -3069,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>719.6225807180064</v>
+        <v>328.9706110579117</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3078,7 +3078,7 @@
         <v>204.8481678023229</v>
       </c>
       <c r="T32" t="n">
-        <v>295.0129731139785</v>
+        <v>296.6755817285639</v>
       </c>
       <c r="U32" t="n">
         <v>359.2212965486107</v>
@@ -3212,28 +3212,28 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>133.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>230.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>281.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>52.36893078764645</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>435.839266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>207.0725306595261</v>
+        <v>436.6021279811511</v>
       </c>
       <c r="S34" t="n">
-        <v>72.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>191.9993129555745</v>
+        <v>182.5751043410117</v>
       </c>
       <c r="C35" t="n">
         <v>159.4745782429939</v>
@@ -3285,19 +3285,19 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>378.7382696589336</v>
+        <v>376.7382696589336</v>
       </c>
       <c r="K35" t="n">
-        <v>102.400690030632</v>
+        <v>772</v>
       </c>
       <c r="L35" t="n">
-        <v>774</v>
+        <v>394.541250755736</v>
       </c>
       <c r="M35" t="n">
-        <v>257.9910820919849</v>
+        <v>772</v>
       </c>
       <c r="N35" t="n">
-        <v>562.7048634595599</v>
+        <v>152.5855355810472</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -3306,13 +3306,13 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>330.9706110579117</v>
+        <v>328.9706110579117</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>203.1855591877378</v>
+        <v>204.8481678023229</v>
       </c>
       <c r="T35" t="n">
         <v>296.6755817285639</v>
@@ -3455,7 +3455,7 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>281.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -3464,13 +3464,13 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>207.0231219415596</v>
+        <v>435.839266425598</v>
       </c>
       <c r="R37" t="n">
         <v>436.6021279811511</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>52.3689307876465</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>191.9993129555745</v>
+        <v>182.5751043409888</v>
       </c>
       <c r="C38" t="n">
         <v>159.4745782429939</v>
@@ -3522,19 +3522,19 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>378.7382696589336</v>
+        <v>376.7382696589336</v>
       </c>
       <c r="K38" t="n">
-        <v>774</v>
+        <v>556.7048634595733</v>
       </c>
       <c r="L38" t="n">
-        <v>102.400690030632</v>
+        <v>506.4308407844114</v>
       </c>
       <c r="M38" t="n">
-        <v>257.9910820919849</v>
+        <v>255.9910820919849</v>
       </c>
       <c r="N38" t="n">
-        <v>154.5855355810472</v>
+        <v>772</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -3543,7 +3543,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>739.0899389364242</v>
+        <v>328.9706110579117</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -3558,7 +3558,7 @@
         <v>359.2212965486107</v>
       </c>
       <c r="V38" t="n">
-        <v>338.1884155522384</v>
+        <v>339.8510241668239</v>
       </c>
       <c r="W38" t="n">
         <v>348.3734759809475</v>
@@ -3695,16 +3695,16 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>91.52316144052003</v>
       </c>
       <c r="P40" t="n">
-        <v>52.36893078764645</v>
+        <v>397.4478973282775</v>
       </c>
       <c r="Q40" t="n">
         <v>435.839266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>436.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3735,25 +3735,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>272.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>240.4745782429939</v>
+        <v>239.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>120.4532149710316</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>194.3632896068686</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>194.7573722870162</v>
+        <v>129.9039587961825</v>
       </c>
       <c r="H41" t="n">
-        <v>199.0096587035274</v>
+        <v>198.0096587035274</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3783,28 +3783,28 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>40.87859882829446</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>284.8481678023229</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>376.6755817285639</v>
       </c>
       <c r="U41" t="n">
-        <v>440.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>420.8510241668239</v>
+        <v>419.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>429.3734759809475</v>
+        <v>428.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>383.2818334606677</v>
+        <v>382.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>302.3174326828064</v>
+        <v>301.3174326828064</v>
       </c>
     </row>
     <row r="42">
@@ -3814,28 +3814,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>175.5565566463266</v>
+        <v>174.5565566463266</v>
       </c>
       <c r="C42" t="n">
-        <v>152.0999124455193</v>
+        <v>151.0999124455193</v>
       </c>
       <c r="D42" t="n">
-        <v>138.9376868977026</v>
+        <v>137.9376868977026</v>
       </c>
       <c r="E42" t="n">
-        <v>133.6720972219126</v>
+        <v>132.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>130.6362423378769</v>
+        <v>129.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>116.7395358750273</v>
+        <v>115.7395358750273</v>
       </c>
       <c r="H42" t="n">
-        <v>123.1680871864211</v>
+        <v>122.1680871864211</v>
       </c>
       <c r="I42" t="n">
-        <v>8.126385891348534</v>
+        <v>7.126385891348534</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3862,28 +3862,28 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>338.2737972923793</v>
+        <v>115.48503914998</v>
       </c>
       <c r="S42" t="n">
-        <v>231.0297743546816</v>
+        <v>256.5639999646113</v>
       </c>
       <c r="T42" t="n">
-        <v>196.3577652175138</v>
+        <v>195.3577652175138</v>
       </c>
       <c r="U42" t="n">
-        <v>191.2103597601867</v>
+        <v>190.2103597601867</v>
       </c>
       <c r="V42" t="n">
-        <v>205.5106671915202</v>
+        <v>204.5106671915202</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>222.3731429098285</v>
       </c>
       <c r="X42" t="n">
-        <v>210.8627394453875</v>
+        <v>209.8627394453875</v>
       </c>
       <c r="Y42" t="n">
-        <v>190.3913927661343</v>
+        <v>189.3913927661343</v>
       </c>
     </row>
     <row r="43">
@@ -3911,7 +3911,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>19.77112610161862</v>
+        <v>18.77112610161862</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -3947,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>1.024566506257713</v>
+        <v>0.02456650625771317</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -3956,7 +3956,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>17.37280983870968</v>
+        <v>16.37280983870968</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
@@ -3972,25 +3972,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>125.9177996917294</v>
       </c>
       <c r="C44" t="n">
-        <v>281.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>242.3391557398498</v>
+        <v>246.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>236.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>236.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>240.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4020,28 +4020,28 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>82.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>397.3945367722125</v>
+        <v>422.6755817285639</v>
       </c>
       <c r="U44" t="n">
-        <v>481.2212965486107</v>
+        <v>485.2212965486107</v>
       </c>
       <c r="V44" t="n">
-        <v>461.8510241668239</v>
+        <v>465.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>474.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>428.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>343.3174326828064</v>
+        <v>347.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -4051,28 +4051,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>220.5565566463266</v>
       </c>
       <c r="C45" t="n">
-        <v>193.0999124455193</v>
+        <v>197.0999124455193</v>
       </c>
       <c r="D45" t="n">
-        <v>179.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>174.6720972219126</v>
+        <v>178.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>175.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>157.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>164.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>49.12638589134853</v>
+        <v>53.12638589134853</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,31 +4096,31 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>9.079265090479588</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>278.1314247157496</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>237.3577652175138</v>
+        <v>241.3577652175138</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>236.2103597601867</v>
       </c>
       <c r="V45" t="n">
-        <v>246.5106671915202</v>
+        <v>250.5106671915202</v>
       </c>
       <c r="W45" t="n">
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>251.8627394453875</v>
+        <v>255.8627394453875</v>
       </c>
       <c r="Y45" t="n">
-        <v>231.3913927661343</v>
+        <v>235.3913927661343</v>
       </c>
     </row>
     <row r="46">
@@ -4151,7 +4151,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>12.63345562011827</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4184,16 +4184,16 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>46.02456650625771</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>15.30444385230164</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>62.37280983870968</v>
       </c>
       <c r="X46" t="n">
         <v>0</v>
@@ -4297,76 +4297,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1106.528124213083</v>
+        <v>1106.448124213083</v>
       </c>
       <c r="C2" t="n">
-        <v>1056.553802755514</v>
+        <v>1056.473802755514</v>
       </c>
       <c r="D2" t="n">
-        <v>1046.1102110991</v>
+        <v>1046.0302110991</v>
       </c>
       <c r="E2" t="n">
-        <v>1041.702847859838</v>
+        <v>1041.622847859839</v>
       </c>
       <c r="F2" t="n">
-        <v>1036.763828962857</v>
+        <v>632.6434249224528</v>
       </c>
       <c r="G2" t="n">
-        <v>628.9280993800121</v>
+        <v>628.8480993800122</v>
       </c>
       <c r="H2" t="n">
-        <v>216.7971309926107</v>
+        <v>216.7171309926107</v>
       </c>
       <c r="I2" t="n">
-        <v>65.2</v>
+        <v>65.12</v>
       </c>
       <c r="J2" t="n">
-        <v>448.0719498394611</v>
+        <v>448.0120508495621</v>
       </c>
       <c r="K2" t="n">
-        <v>1155.805906933501</v>
+        <v>741.0033264140369</v>
       </c>
       <c r="L2" t="n">
-        <v>1930.985114233068</v>
+        <v>724.6411041918145</v>
       </c>
       <c r="M2" t="n">
-        <v>2054.792536422134</v>
+        <v>1229.500011169607</v>
       </c>
       <c r="N2" t="n">
-        <v>2038.41021318981</v>
+        <v>1213.137788947385</v>
       </c>
       <c r="O2" t="n">
-        <v>2022.027889957487</v>
+        <v>2018.997788947385</v>
       </c>
       <c r="P2" t="n">
-        <v>2828.877889957487</v>
+        <v>2824.857788947385</v>
       </c>
       <c r="Q2" t="n">
-        <v>3260</v>
+        <v>3256</v>
       </c>
       <c r="R2" t="n">
-        <v>3006.587273910814</v>
+        <v>3002.587273910814</v>
       </c>
       <c r="S2" t="n">
-        <v>2506.740639767053</v>
+        <v>2502.740639767053</v>
       </c>
       <c r="T2" t="n">
-        <v>2220.714362390286</v>
+        <v>2220.634362390286</v>
       </c>
       <c r="U2" t="n">
-        <v>1968.975679007851</v>
+        <v>1968.895679007851</v>
       </c>
       <c r="V2" t="n">
-        <v>1736.80292732419</v>
+        <v>1736.722927324191</v>
       </c>
       <c r="W2" t="n">
-        <v>1496.021638454547</v>
+        <v>1495.941638454547</v>
       </c>
       <c r="X2" t="n">
-        <v>1301.797564251852</v>
+        <v>1301.717564251852</v>
       </c>
       <c r="Y2" t="n">
-        <v>1189.355713057098</v>
+        <v>1189.275713057098</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>931.5895195792149</v>
+        <v>740.2832657544849</v>
       </c>
       <c r="C3" t="n">
-        <v>566.8421332706096</v>
+        <v>740.2832657544849</v>
       </c>
       <c r="D3" t="n">
-        <v>566.8421332706096</v>
+        <v>740.2832657544849</v>
       </c>
       <c r="E3" t="n">
-        <v>566.8421332706096</v>
+        <v>394.1498342171994</v>
       </c>
       <c r="F3" t="n">
-        <v>223.7752218182086</v>
+        <v>394.1498342171994</v>
       </c>
       <c r="G3" t="n">
-        <v>65.2</v>
+        <v>65.12</v>
       </c>
       <c r="H3" t="n">
-        <v>65.2</v>
+        <v>65.12</v>
       </c>
       <c r="I3" t="n">
-        <v>65.2</v>
+        <v>65.12</v>
       </c>
       <c r="J3" t="n">
-        <v>189.156520175299</v>
+        <v>189.076520175299</v>
       </c>
       <c r="K3" t="n">
-        <v>378.3493362696823</v>
+        <v>378.2693362696824</v>
       </c>
       <c r="L3" t="n">
-        <v>649.6997978648824</v>
+        <v>649.6197978648825</v>
       </c>
       <c r="M3" t="n">
-        <v>735.7803396077417</v>
+        <v>735.7003396077417</v>
       </c>
       <c r="N3" t="n">
-        <v>869.06062421531</v>
+        <v>868.9806242153101</v>
       </c>
       <c r="O3" t="n">
-        <v>1108.103075899029</v>
+        <v>1108.023075899029</v>
       </c>
       <c r="P3" t="n">
-        <v>1220.632420368536</v>
+        <v>1220.552420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1220.632420368536</v>
+        <v>1220.552420368536</v>
       </c>
       <c r="R3" t="n">
-        <v>1071.871008962092</v>
+        <v>1071.791008962092</v>
       </c>
       <c r="S3" t="n">
-        <v>1004.634645361474</v>
+        <v>1004.554645361474</v>
       </c>
       <c r="T3" t="n">
-        <v>999.2227613033796</v>
+        <v>807.9165074786496</v>
       </c>
       <c r="U3" t="n">
-        <v>999.0102766971303</v>
+        <v>807.7040228724003</v>
       </c>
       <c r="V3" t="n">
-        <v>984.3530371097362</v>
+        <v>793.0467832850062</v>
       </c>
       <c r="W3" t="n">
-        <v>951.6528927563741</v>
+        <v>760.3466389316441</v>
       </c>
       <c r="X3" t="n">
-        <v>931.5895195792149</v>
+        <v>740.2832657544849</v>
       </c>
       <c r="Y3" t="n">
-        <v>931.5895195792149</v>
+        <v>740.2832657544849</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>847.6558574435028</v>
+        <v>1064.911087184361</v>
       </c>
       <c r="C4" t="n">
-        <v>973.6578632619386</v>
+        <v>1190.913093002797</v>
       </c>
       <c r="D4" t="n">
-        <v>973.6578632619386</v>
+        <v>1304.232237127797</v>
       </c>
       <c r="E4" t="n">
-        <v>973.6578632619386</v>
+        <v>1422.06114133921</v>
       </c>
       <c r="F4" t="n">
-        <v>1098.018835853874</v>
+        <v>1546.422113931146</v>
       </c>
       <c r="G4" t="n">
-        <v>1244.509930203872</v>
+        <v>1546.422113931146</v>
       </c>
       <c r="H4" t="n">
-        <v>1244.509930203872</v>
+        <v>1546.422113931146</v>
       </c>
       <c r="I4" t="n">
-        <v>1465.642809139955</v>
+        <v>1546.422113931146</v>
       </c>
       <c r="J4" t="n">
-        <v>1465.642809139955</v>
+        <v>1546.422113931146</v>
       </c>
       <c r="K4" t="n">
-        <v>1576.007243076824</v>
+        <v>1546.422113931146</v>
       </c>
       <c r="L4" t="n">
-        <v>1552.221760089168</v>
+        <v>1546.422113931146</v>
       </c>
       <c r="M4" t="n">
-        <v>1430.37164756134</v>
+        <v>1424.572001403317</v>
       </c>
       <c r="N4" t="n">
-        <v>1257.457430115193</v>
+        <v>1251.657783957171</v>
       </c>
       <c r="O4" t="n">
-        <v>1014.583122964673</v>
+        <v>1008.783476806651</v>
       </c>
       <c r="P4" t="n">
-        <v>724.2317115219688</v>
+        <v>718.4320653639461</v>
       </c>
       <c r="Q4" t="n">
-        <v>395.1011393749001</v>
+        <v>389.3014932168774</v>
       </c>
       <c r="R4" t="n">
-        <v>65.2</v>
+        <v>65.12</v>
       </c>
       <c r="S4" t="n">
-        <v>102.4502550941731</v>
+        <v>65.12</v>
       </c>
       <c r="T4" t="n">
-        <v>290.525934252978</v>
+        <v>245.3410722906108</v>
       </c>
       <c r="U4" t="n">
-        <v>537.0771268912647</v>
+        <v>491.8922649288975</v>
       </c>
       <c r="V4" t="n">
-        <v>735.8985197772106</v>
+        <v>690.7136578148434</v>
       </c>
       <c r="W4" t="n">
-        <v>735.8985197772106</v>
+        <v>690.7136578148434</v>
       </c>
       <c r="X4" t="n">
-        <v>735.8985197772106</v>
+        <v>841.7444488390369</v>
       </c>
       <c r="Y4" t="n">
-        <v>735.8985197772106</v>
+        <v>953.1537495180692</v>
       </c>
     </row>
     <row r="5">
@@ -4549,7 +4549,7 @@
         <v>730.1885086340035</v>
       </c>
       <c r="G5" t="n">
-        <v>628.9280993800121</v>
+        <v>322.3527790511588</v>
       </c>
       <c r="H5" t="n">
         <v>216.7971309926107</v>
@@ -4558,22 +4558,22 @@
         <v>65.2</v>
       </c>
       <c r="J5" t="n">
-        <v>65.2</v>
+        <v>448.0719498394611</v>
       </c>
       <c r="K5" t="n">
-        <v>441.0925364221338</v>
+        <v>1156.448952311256</v>
       </c>
       <c r="L5" t="n">
-        <v>1247.942536422134</v>
+        <v>1140.066629078932</v>
       </c>
       <c r="M5" t="n">
-        <v>1231.56021318981</v>
+        <v>1429.121360241373</v>
       </c>
       <c r="N5" t="n">
-        <v>1215.177889957487</v>
+        <v>2038.41021318981</v>
       </c>
       <c r="O5" t="n">
-        <v>2022.027889957487</v>
+        <v>2845.26021318981</v>
       </c>
       <c r="P5" t="n">
         <v>2828.877889957487</v>
@@ -4588,7 +4588,7 @@
         <v>2506.740639767053</v>
       </c>
       <c r="T5" t="n">
-        <v>1914.139042061433</v>
+        <v>2318.179446101837</v>
       </c>
       <c r="U5" t="n">
         <v>1662.400358678998</v>
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>139.10814922939</v>
+        <v>931.5895195792149</v>
       </c>
       <c r="C6" t="n">
-        <v>139.10814922939</v>
+        <v>931.5895195792149</v>
       </c>
       <c r="D6" t="n">
-        <v>65.2</v>
+        <v>931.5895195792149</v>
       </c>
       <c r="E6" t="n">
-        <v>65.2</v>
+        <v>613.5494159256323</v>
       </c>
       <c r="F6" t="n">
-        <v>65.2</v>
+        <v>613.5494159256323</v>
       </c>
       <c r="G6" t="n">
-        <v>65.2</v>
+        <v>284.5195817084329</v>
       </c>
       <c r="H6" t="n">
-        <v>65.2</v>
+        <v>284.5195817084329</v>
       </c>
       <c r="I6" t="n">
         <v>65.2</v>
@@ -4670,19 +4670,19 @@
         <v>999.2227613033796</v>
       </c>
       <c r="U6" t="n">
-        <v>594.9698726567262</v>
+        <v>999.0102766971303</v>
       </c>
       <c r="V6" t="n">
-        <v>580.3126330693322</v>
+        <v>984.3530371097362</v>
       </c>
       <c r="W6" t="n">
-        <v>547.61248871597</v>
+        <v>951.6528927563741</v>
       </c>
       <c r="X6" t="n">
-        <v>527.5491155388108</v>
+        <v>931.5895195792149</v>
       </c>
       <c r="Y6" t="n">
-        <v>527.5491155388108</v>
+        <v>931.5895195792149</v>
       </c>
     </row>
     <row r="7">
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1281.986867406406</v>
+        <v>948.991339226039</v>
       </c>
       <c r="C7" t="n">
-        <v>1407.988873224842</v>
+        <v>1074.993345044475</v>
       </c>
       <c r="D7" t="n">
-        <v>1521.308017349842</v>
+        <v>1074.993345044475</v>
       </c>
       <c r="E7" t="n">
-        <v>1576.007243076824</v>
+        <v>1074.993345044475</v>
       </c>
       <c r="F7" t="n">
-        <v>1576.007243076824</v>
+        <v>1074.993345044475</v>
       </c>
       <c r="G7" t="n">
-        <v>1576.007243076824</v>
+        <v>1074.993345044475</v>
       </c>
       <c r="H7" t="n">
-        <v>1576.007243076824</v>
+        <v>1244.509930203872</v>
       </c>
       <c r="I7" t="n">
-        <v>1576.007243076824</v>
+        <v>1465.642809139955</v>
       </c>
       <c r="J7" t="n">
-        <v>1576.007243076824</v>
+        <v>1465.642809139955</v>
       </c>
       <c r="K7" t="n">
         <v>1576.007243076824</v>
@@ -4743,25 +4743,25 @@
         <v>65.2</v>
       </c>
       <c r="S7" t="n">
-        <v>102.4502550941731</v>
+        <v>65.2</v>
       </c>
       <c r="T7" t="n">
-        <v>290.525934252978</v>
+        <v>65.2</v>
       </c>
       <c r="U7" t="n">
-        <v>537.0771268912647</v>
+        <v>204.0815987108978</v>
       </c>
       <c r="V7" t="n">
-        <v>735.8985197772106</v>
+        <v>402.9029915968438</v>
       </c>
       <c r="W7" t="n">
-        <v>907.789438036888</v>
+        <v>574.7939098565212</v>
       </c>
       <c r="X7" t="n">
-        <v>1058.820229061082</v>
+        <v>725.8247008807147</v>
       </c>
       <c r="Y7" t="n">
-        <v>1170.229529740114</v>
+        <v>837.234001559747</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1457.405934013821</v>
+        <v>649.3251259330123</v>
       </c>
       <c r="C8" t="n">
-        <v>1003.391208515847</v>
+        <v>599.3508044754426</v>
       </c>
       <c r="D8" t="n">
-        <v>588.9072128190289</v>
+        <v>588.9072128190287</v>
       </c>
       <c r="E8" t="n">
-        <v>584.4998495797677</v>
+        <v>584.4998495797674</v>
       </c>
       <c r="F8" t="n">
-        <v>579.560830682786</v>
+        <v>579.5608306827858</v>
       </c>
       <c r="G8" t="n">
-        <v>575.7655051403453</v>
+        <v>224.8876953396081</v>
       </c>
       <c r="H8" t="n">
         <v>216.7971309926107</v>
@@ -4798,16 +4798,16 @@
         <v>448.0719498394611</v>
       </c>
       <c r="K8" t="n">
-        <v>1156.448952311255</v>
+        <v>1155.805906933501</v>
       </c>
       <c r="L8" t="n">
-        <v>1963.298952311255</v>
+        <v>1549.953730454442</v>
       </c>
       <c r="M8" t="n">
-        <v>1946.916629078931</v>
+        <v>2054.792536422134</v>
       </c>
       <c r="N8" t="n">
-        <v>2556.205482027368</v>
+        <v>2038.41021318981</v>
       </c>
       <c r="O8" t="n">
         <v>2845.26021318981</v>
@@ -4822,25 +4822,25 @@
         <v>3260</v>
       </c>
       <c r="S8" t="n">
-        <v>2760.153365856239</v>
+        <v>3164.193769896644</v>
       </c>
       <c r="T8" t="n">
-        <v>2571.592172191023</v>
+        <v>2975.632576231427</v>
       </c>
       <c r="U8" t="n">
-        <v>2319.853488808588</v>
+        <v>2723.893892848992</v>
       </c>
       <c r="V8" t="n">
-        <v>2087.680737124928</v>
+        <v>2491.721141165332</v>
       </c>
       <c r="W8" t="n">
         <v>1846.899448255284</v>
       </c>
       <c r="X8" t="n">
-        <v>1652.675374052589</v>
+        <v>1248.634970012185</v>
       </c>
       <c r="Y8" t="n">
-        <v>1540.233522857835</v>
+        <v>732.152714777027</v>
       </c>
     </row>
     <row r="9">
@@ -4850,16 +4850,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>931.5895195792149</v>
+        <v>124.1234662800891</v>
       </c>
       <c r="C9" t="n">
-        <v>931.5895195792149</v>
+        <v>124.1234662800891</v>
       </c>
       <c r="D9" t="n">
-        <v>754.4003429896864</v>
+        <v>124.1234662800891</v>
       </c>
       <c r="E9" t="n">
-        <v>408.2669114524009</v>
+        <v>65.2</v>
       </c>
       <c r="F9" t="n">
         <v>65.2</v>
@@ -4913,13 +4913,13 @@
         <v>984.3530371097362</v>
       </c>
       <c r="W9" t="n">
-        <v>951.6528927563741</v>
+        <v>547.6124887159699</v>
       </c>
       <c r="X9" t="n">
-        <v>931.5895195792149</v>
+        <v>527.5491155388107</v>
       </c>
       <c r="Y9" t="n">
-        <v>931.5895195792149</v>
+        <v>124.1234662800891</v>
       </c>
     </row>
     <row r="10">
@@ -4929,19 +4929,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1056.660933153428</v>
+        <v>1244.736612312233</v>
       </c>
       <c r="C10" t="n">
-        <v>1182.662938971864</v>
+        <v>1370.738618130669</v>
       </c>
       <c r="D10" t="n">
-        <v>1295.982083096864</v>
+        <v>1484.057762255669</v>
       </c>
       <c r="E10" t="n">
-        <v>1413.810987308277</v>
+        <v>1576.007243076824</v>
       </c>
       <c r="F10" t="n">
-        <v>1538.171959900212</v>
+        <v>1576.007243076824</v>
       </c>
       <c r="G10" t="n">
         <v>1576.007243076824</v>
@@ -4983,22 +4983,22 @@
         <v>65.2</v>
       </c>
       <c r="T10" t="n">
-        <v>65.2</v>
+        <v>253.2756791588048</v>
       </c>
       <c r="U10" t="n">
-        <v>311.7511926382866</v>
+        <v>499.8268717970915</v>
       </c>
       <c r="V10" t="n">
-        <v>510.5725855242326</v>
+        <v>698.6482646830375</v>
       </c>
       <c r="W10" t="n">
-        <v>682.46350378391</v>
+        <v>870.5391829427149</v>
       </c>
       <c r="X10" t="n">
-        <v>833.4942948081035</v>
+        <v>1021.569973966908</v>
       </c>
       <c r="Y10" t="n">
-        <v>944.9035954871358</v>
+        <v>1132.979274645941</v>
       </c>
     </row>
     <row r="11">
@@ -5008,22 +5008,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1207.456245745725</v>
+        <v>479.1532666493371</v>
       </c>
       <c r="C11" t="n">
-        <v>980.7142475204787</v>
+        <v>252.4112684240907</v>
       </c>
       <c r="D11" t="n">
-        <v>793.502979096388</v>
+        <v>65.2</v>
       </c>
       <c r="E11" t="n">
-        <v>612.32793908945</v>
+        <v>65.2</v>
       </c>
       <c r="F11" t="n">
-        <v>430.6212434247915</v>
+        <v>65.2</v>
       </c>
       <c r="G11" t="n">
-        <v>250.0582411146742</v>
+        <v>65.2</v>
       </c>
       <c r="H11" t="n">
         <v>65.2</v>
@@ -5038,19 +5038,19 @@
         <v>1166.215479385524</v>
       </c>
       <c r="L11" t="n">
-        <v>1973.065479385524</v>
+        <v>1166.215479385524</v>
       </c>
       <c r="M11" t="n">
-        <v>2483.914308114459</v>
+        <v>1677.064308114459</v>
       </c>
       <c r="N11" t="n">
-        <v>3097.134627889222</v>
+        <v>2290.284627889223</v>
       </c>
       <c r="O11" t="n">
-        <v>3260</v>
+        <v>2290.284627889223</v>
       </c>
       <c r="P11" t="n">
-        <v>3260</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="Q11" t="n">
         <v>3260</v>
@@ -5059,25 +5059,25 @@
         <v>3233.860001183541</v>
       </c>
       <c r="S11" t="n">
-        <v>3233.860001183541</v>
+        <v>3019.274435865494</v>
       </c>
       <c r="T11" t="n">
-        <v>3233.860001183541</v>
+        <v>2653.945565432601</v>
       </c>
       <c r="U11" t="n">
-        <v>2805.353641033429</v>
+        <v>2225.439205282489</v>
       </c>
       <c r="V11" t="n">
-        <v>2544.801755927539</v>
+        <v>1816.498776831151</v>
       </c>
       <c r="W11" t="n">
-        <v>2127.252790290219</v>
+        <v>1398.949811193831</v>
       </c>
       <c r="X11" t="n">
-        <v>1756.261039319847</v>
+        <v>1027.958060223459</v>
       </c>
       <c r="Y11" t="n">
-        <v>1467.051511357417</v>
+        <v>738.7485322610286</v>
       </c>
     </row>
     <row r="12">
@@ -5114,10 +5114,10 @@
         <v>419.7013981428639</v>
       </c>
       <c r="K12" t="n">
-        <v>627.8199167834982</v>
+        <v>831.6442142372473</v>
       </c>
       <c r="L12" t="n">
-        <v>1121.920378378698</v>
+        <v>1325.744675832447</v>
       </c>
       <c r="M12" t="n">
         <v>1430.750920121558</v>
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>86.83751944022833</v>
+        <v>177.5115880782802</v>
       </c>
       <c r="C13" t="n">
-        <v>86.83751944022833</v>
+        <v>177.5115880782802</v>
       </c>
       <c r="D13" t="n">
-        <v>69.00921828446326</v>
+        <v>177.5115880782802</v>
       </c>
       <c r="E13" t="n">
-        <v>69.00921828446326</v>
+        <v>177.5115880782802</v>
       </c>
       <c r="F13" t="n">
-        <v>69.00921828446326</v>
+        <v>177.5115880782802</v>
       </c>
       <c r="G13" t="n">
-        <v>69.00921828446326</v>
+        <v>177.5115880782802</v>
       </c>
       <c r="H13" t="n">
+        <v>173.7023697938169</v>
+      </c>
+      <c r="I13" t="n">
+        <v>221.5852487298998</v>
+      </c>
+      <c r="J13" t="n">
+        <v>409.4189893823511</v>
+      </c>
+      <c r="K13" t="n">
+        <v>409.4189893823511</v>
+      </c>
+      <c r="L13" t="n">
+        <v>409.4189893823511</v>
+      </c>
+      <c r="M13" t="n">
+        <v>409.4189893823511</v>
+      </c>
+      <c r="N13" t="n">
+        <v>409.4189893823511</v>
+      </c>
+      <c r="O13" t="n">
+        <v>409.4189893823511</v>
+      </c>
+      <c r="P13" t="n">
+        <v>409.4189893823511</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>409.4189893823511</v>
+      </c>
+      <c r="R13" t="n">
         <v>65.2</v>
       </c>
-      <c r="I13" t="n">
-        <v>113.0828789360829</v>
-      </c>
-      <c r="J13" t="n">
-        <v>300.9166195885342</v>
-      </c>
-      <c r="K13" t="n">
-        <v>300.9166195885342</v>
-      </c>
-      <c r="L13" t="n">
-        <v>100.3634598332017</v>
-      </c>
-      <c r="M13" t="n">
-        <v>100.3634598332017</v>
-      </c>
-      <c r="N13" t="n">
-        <v>100.3634598332017</v>
-      </c>
-      <c r="O13" t="n">
-        <v>100.3634598332017</v>
-      </c>
-      <c r="P13" t="n">
-        <v>100.3634598332017</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>100.3634598332017</v>
-      </c>
-      <c r="R13" t="n">
-        <v>100.3634598332017</v>
-      </c>
       <c r="S13" t="n">
-        <v>100.3634598332017</v>
+        <v>65.2</v>
       </c>
       <c r="T13" t="n">
-        <v>115.1891389920066</v>
+        <v>80.02567915880486</v>
       </c>
       <c r="U13" t="n">
-        <v>188.4903316302932</v>
+        <v>153.3268717970915</v>
       </c>
       <c r="V13" t="n">
-        <v>214.0617245162392</v>
+        <v>178.8982646830374</v>
       </c>
       <c r="W13" t="n">
-        <v>212.6750479114819</v>
+        <v>177.5115880782802</v>
       </c>
       <c r="X13" t="n">
-        <v>212.6750479114819</v>
+        <v>177.5115880782802</v>
       </c>
       <c r="Y13" t="n">
-        <v>149.578731901924</v>
+        <v>177.5115880782802</v>
       </c>
     </row>
     <row r="14">
@@ -5272,22 +5272,22 @@
         <v>456.5091130376557</v>
       </c>
       <c r="K14" t="n">
-        <v>456.5091130376557</v>
+        <v>1166.215479385524</v>
       </c>
       <c r="L14" t="n">
-        <v>456.5091130376557</v>
+        <v>1166.215479385524</v>
       </c>
       <c r="M14" t="n">
-        <v>967.3579417665908</v>
+        <v>1166.215479385524</v>
       </c>
       <c r="N14" t="n">
-        <v>1580.578261541354</v>
+        <v>1207.700904947333</v>
       </c>
       <c r="O14" t="n">
-        <v>2387.428261541354</v>
+        <v>2014.550904947333</v>
       </c>
       <c r="P14" t="n">
-        <v>3194.278261541354</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="Q14" t="n">
         <v>3260</v>
@@ -5348,22 +5348,22 @@
         <v>98.73487796756496</v>
       </c>
       <c r="J15" t="n">
-        <v>222.6913981428639</v>
+        <v>471.1813981428639</v>
       </c>
       <c r="K15" t="n">
-        <v>411.8842142372473</v>
+        <v>908.8642142372473</v>
       </c>
       <c r="L15" t="n">
-        <v>683.2346758324475</v>
+        <v>1428.704675832447</v>
       </c>
       <c r="M15" t="n">
-        <v>933.8515261821633</v>
+        <v>1679.321526182163</v>
       </c>
       <c r="N15" t="n">
-        <v>1315.621810789732</v>
+        <v>1812.601810789732</v>
       </c>
       <c r="O15" t="n">
-        <v>1803.15426247345</v>
+        <v>2051.64426247345</v>
       </c>
       <c r="P15" t="n">
         <v>2164.173606942957</v>
@@ -5439,10 +5439,10 @@
         <v>599.1197446017254</v>
       </c>
       <c r="N16" t="n">
-        <v>275.7004766505285</v>
+        <v>599.1197446017254</v>
       </c>
       <c r="O16" t="n">
-        <v>65.2</v>
+        <v>506.0564619477551</v>
       </c>
       <c r="P16" t="n">
         <v>65.2</v>
@@ -5494,13 +5494,13 @@
         <v>452.1766172565348</v>
       </c>
       <c r="F17" t="n">
-        <v>325.0153761373309</v>
+        <v>321.5303343338825</v>
       </c>
       <c r="G17" t="n">
-        <v>198.9978283726681</v>
+        <v>195.5127865692196</v>
       </c>
       <c r="H17" t="n">
-        <v>68.68504180344846</v>
+        <v>65.2</v>
       </c>
       <c r="I17" t="n">
         <v>65.2</v>
@@ -5509,22 +5509,22 @@
         <v>456.5091130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>456.5091130376557</v>
+        <v>1166.215479385524</v>
       </c>
       <c r="L17" t="n">
-        <v>456.5091130376557</v>
+        <v>1166.215479385524</v>
       </c>
       <c r="M17" t="n">
-        <v>594.4805851725695</v>
+        <v>1677.064308114459</v>
       </c>
       <c r="N17" t="n">
-        <v>1207.700904947333</v>
+        <v>2290.284627889223</v>
       </c>
       <c r="O17" t="n">
-        <v>2014.550904947333</v>
+        <v>2290.284627889223</v>
       </c>
       <c r="P17" t="n">
-        <v>2821.400904947332</v>
+        <v>3097.134627889222</v>
       </c>
       <c r="Q17" t="n">
         <v>3260</v>
@@ -5582,28 +5582,28 @@
         <v>65.2</v>
       </c>
       <c r="I18" t="n">
-        <v>126.454877967565</v>
+        <v>65.2</v>
       </c>
       <c r="J18" t="n">
-        <v>250.4113981428639</v>
+        <v>189.156520175299</v>
       </c>
       <c r="K18" t="n">
-        <v>698.5796261621044</v>
+        <v>378.3493362696823</v>
       </c>
       <c r="L18" t="n">
-        <v>969.9300877573045</v>
+        <v>649.6997978648824</v>
       </c>
       <c r="M18" t="n">
-        <v>1056.010629500164</v>
+        <v>735.7803396077417</v>
       </c>
       <c r="N18" t="n">
-        <v>1189.290914107732</v>
+        <v>869.06062421531</v>
       </c>
       <c r="O18" t="n">
-        <v>1428.333365791451</v>
+        <v>1323.471838231026</v>
       </c>
       <c r="P18" t="n">
-        <v>1817.072710260958</v>
+        <v>1712.211182700533</v>
       </c>
       <c r="Q18" t="n">
         <v>1817.072710260958</v>
@@ -5679,13 +5679,13 @@
         <v>859.3827230120968</v>
       </c>
       <c r="O19" t="n">
-        <v>494.2861936393544</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="P19" t="n">
-        <v>81.71255997442762</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="Q19" t="n">
-        <v>65.2</v>
+        <v>517.3233615971224</v>
       </c>
       <c r="R19" t="n">
         <v>65.2</v>
@@ -5737,28 +5737,28 @@
         <v>198.9978283726681</v>
       </c>
       <c r="H20" t="n">
-        <v>65.2</v>
+        <v>68.68504180344846</v>
       </c>
       <c r="I20" t="n">
         <v>65.2</v>
       </c>
       <c r="J20" t="n">
-        <v>65.2</v>
+        <v>456.5091130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>774.9063663478685</v>
+        <v>456.5091130376557</v>
       </c>
       <c r="L20" t="n">
-        <v>1581.756366347868</v>
+        <v>696.8520762183977</v>
       </c>
       <c r="M20" t="n">
-        <v>2092.605195076803</v>
+        <v>1207.700904947333</v>
       </c>
       <c r="N20" t="n">
-        <v>2705.825514851566</v>
+        <v>1207.700904947333</v>
       </c>
       <c r="O20" t="n">
-        <v>2821.400904947332</v>
+        <v>2014.550904947333</v>
       </c>
       <c r="P20" t="n">
         <v>2821.400904947332</v>
@@ -5825,22 +5825,22 @@
         <v>250.4113981428639</v>
       </c>
       <c r="K21" t="n">
-        <v>715.8142142372474</v>
+        <v>439.6042142372473</v>
       </c>
       <c r="L21" t="n">
-        <v>987.1646758324475</v>
+        <v>710.9546758324475</v>
       </c>
       <c r="M21" t="n">
-        <v>1332.220629500164</v>
+        <v>797.0352175753068</v>
       </c>
       <c r="N21" t="n">
-        <v>1465.500914107732</v>
+        <v>1084.429386547307</v>
       </c>
       <c r="O21" t="n">
-        <v>1704.543365791451</v>
+        <v>1599.681838231026</v>
       </c>
       <c r="P21" t="n">
-        <v>1817.072710260958</v>
+        <v>1712.211182700533</v>
       </c>
       <c r="Q21" t="n">
         <v>1817.072710260958</v>
@@ -5922,7 +5922,7 @@
         <v>859.3827230120968</v>
       </c>
       <c r="Q22" t="n">
-        <v>408.0299286428058</v>
+        <v>517.3233615971224</v>
       </c>
       <c r="R22" t="n">
         <v>65.2</v>
@@ -5974,25 +5974,25 @@
         <v>198.9978283726681</v>
       </c>
       <c r="H23" t="n">
-        <v>65.2</v>
+        <v>68.68504180344846</v>
       </c>
       <c r="I23" t="n">
         <v>65.2</v>
       </c>
       <c r="J23" t="n">
-        <v>456.5091130376557</v>
+        <v>83.63175644363446</v>
       </c>
       <c r="K23" t="n">
-        <v>456.5091130376557</v>
+        <v>83.63175644363446</v>
       </c>
       <c r="L23" t="n">
-        <v>456.5091130376557</v>
+        <v>83.63175644363446</v>
       </c>
       <c r="M23" t="n">
-        <v>967.3579417665908</v>
+        <v>594.4805851725695</v>
       </c>
       <c r="N23" t="n">
-        <v>1580.578261541354</v>
+        <v>1207.700904947333</v>
       </c>
       <c r="O23" t="n">
         <v>2014.550904947333</v>
@@ -6059,25 +6059,25 @@
         <v>65.2</v>
       </c>
       <c r="J24" t="n">
-        <v>189.156520175299</v>
+        <v>465.3665201752989</v>
       </c>
       <c r="K24" t="n">
-        <v>378.3493362696823</v>
+        <v>930.7693362696823</v>
       </c>
       <c r="L24" t="n">
-        <v>649.6997978648824</v>
+        <v>1202.119797864882</v>
       </c>
       <c r="M24" t="n">
-        <v>735.7803396077417</v>
+        <v>1288.200339607742</v>
       </c>
       <c r="N24" t="n">
-        <v>869.06062421531</v>
+        <v>1421.48062421531</v>
       </c>
       <c r="O24" t="n">
-        <v>1384.313075899029</v>
+        <v>1660.523075899029</v>
       </c>
       <c r="P24" t="n">
-        <v>1712.211182700533</v>
+        <v>1773.052420368535</v>
       </c>
       <c r="Q24" t="n">
         <v>1817.072710260958</v>
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>685.6712852464632</v>
+        <v>615.53620520342</v>
       </c>
       <c r="C26" t="n">
-        <v>458.9292870212168</v>
+        <v>615.53620520342</v>
       </c>
       <c r="D26" t="n">
-        <v>271.718018597126</v>
+        <v>428.3249367793293</v>
       </c>
       <c r="E26" t="n">
-        <v>271.718018597126</v>
+        <v>428.3249367793293</v>
       </c>
       <c r="F26" t="n">
-        <v>271.718018597126</v>
+        <v>246.6182411146709</v>
       </c>
       <c r="G26" t="n">
-        <v>246.7782411146742</v>
+        <v>246.6182411146709</v>
       </c>
       <c r="H26" t="n">
-        <v>61.92</v>
+        <v>61.75999999999669</v>
       </c>
       <c r="I26" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="J26" t="n">
-        <v>61.92</v>
+        <v>453.0691130376557</v>
       </c>
       <c r="K26" t="n">
-        <v>771.6263663478684</v>
+        <v>453.0691130376557</v>
       </c>
       <c r="L26" t="n">
-        <v>1380.292076218353</v>
+        <v>1217.349113037656</v>
       </c>
       <c r="M26" t="n">
-        <v>1891.140904947288</v>
+        <v>1728.197941766591</v>
       </c>
       <c r="N26" t="n">
-        <v>1891.140904947288</v>
+        <v>2341.418261541354</v>
       </c>
       <c r="O26" t="n">
-        <v>1891.140904947288</v>
+        <v>2649.400904947332</v>
       </c>
       <c r="P26" t="n">
-        <v>2657.400904947332</v>
+        <v>2649.400904947332</v>
       </c>
       <c r="Q26" t="n">
-        <v>3096</v>
+        <v>3088</v>
       </c>
       <c r="R26" t="n">
-        <v>3069.860001183541</v>
+        <v>3061.860001183541</v>
       </c>
       <c r="S26" t="n">
-        <v>2797.286094312508</v>
+        <v>2789.286094312508</v>
       </c>
       <c r="T26" t="n">
-        <v>2431.957223879615</v>
+        <v>2423.957223879615</v>
       </c>
       <c r="U26" t="n">
-        <v>2431.957223879615</v>
+        <v>1995.450863729503</v>
       </c>
       <c r="V26" t="n">
-        <v>2023.016795428278</v>
+        <v>1586.510435278166</v>
       </c>
       <c r="W26" t="n">
-        <v>1605.467829790957</v>
+        <v>1168.961469640845</v>
       </c>
       <c r="X26" t="n">
-        <v>1234.476078820585</v>
+        <v>797.9697186704736</v>
       </c>
       <c r="Y26" t="n">
-        <v>945.2665508581547</v>
+        <v>615.53620520342</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>768.2367292570302</v>
+        <v>768.0767292570301</v>
       </c>
       <c r="C27" t="n">
-        <v>630.7620702211522</v>
+        <v>630.6020702211521</v>
       </c>
       <c r="D27" t="n">
-        <v>506.582588506301</v>
+        <v>506.4225885063009</v>
       </c>
       <c r="E27" t="n">
-        <v>387.7218842417428</v>
+        <v>387.5618842417427</v>
       </c>
       <c r="F27" t="n">
-        <v>271.9277000620692</v>
+        <v>271.7677000620691</v>
       </c>
       <c r="G27" t="n">
-        <v>170.1705931175971</v>
+        <v>170.0105931175971</v>
       </c>
       <c r="H27" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="I27" t="n">
-        <v>69.71487796756496</v>
+        <v>69.55487796756495</v>
       </c>
       <c r="J27" t="n">
-        <v>212.5971006891146</v>
+        <v>212.4371006891147</v>
       </c>
       <c r="K27" t="n">
-        <v>624.539916783498</v>
+        <v>624.3799167834982</v>
       </c>
       <c r="L27" t="n">
-        <v>1118.640378378698</v>
+        <v>1118.480378378698</v>
       </c>
       <c r="M27" t="n">
-        <v>1427.470920121557</v>
+        <v>1427.310920121558</v>
       </c>
       <c r="N27" t="n">
-        <v>1783.501204729126</v>
+        <v>1783.341204729126</v>
       </c>
       <c r="O27" t="n">
-        <v>2245.293656412844</v>
+        <v>2245.133656412845</v>
       </c>
       <c r="P27" t="n">
-        <v>2580.573000882351</v>
+        <v>2580.413000882351</v>
       </c>
       <c r="Q27" t="n">
-        <v>2631.974528442776</v>
+        <v>2631.814528442776</v>
       </c>
       <c r="R27" t="n">
-        <v>2306.445440268656</v>
+        <v>2306.285440268656</v>
       </c>
       <c r="S27" t="n">
-        <v>2062.441399900361</v>
+        <v>2062.281399900362</v>
       </c>
       <c r="T27" t="n">
-        <v>1880.26183907459</v>
+        <v>1880.10183907459</v>
       </c>
       <c r="U27" t="n">
-        <v>1703.281677700664</v>
+        <v>1703.121677700664</v>
       </c>
       <c r="V27" t="n">
-        <v>1511.856761345593</v>
+        <v>1511.696761345593</v>
       </c>
       <c r="W27" t="n">
-        <v>1302.388940224554</v>
+        <v>1302.228940224554</v>
       </c>
       <c r="X27" t="n">
-        <v>1105.557890279718</v>
+        <v>1105.397890279718</v>
       </c>
       <c r="Y27" t="n">
-        <v>929.4049682937238</v>
+        <v>929.2449682937237</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>174.2315880782802</v>
+        <v>174.0715880782802</v>
       </c>
       <c r="C28" t="n">
-        <v>174.2315880782802</v>
+        <v>174.0715880782802</v>
       </c>
       <c r="D28" t="n">
-        <v>174.2315880782802</v>
+        <v>174.0715880782802</v>
       </c>
       <c r="E28" t="n">
-        <v>174.2315880782802</v>
+        <v>174.0715880782802</v>
       </c>
       <c r="F28" t="n">
-        <v>174.2315880782802</v>
+        <v>174.0715880782802</v>
       </c>
       <c r="G28" t="n">
-        <v>174.2315880782802</v>
+        <v>174.0715880782802</v>
       </c>
       <c r="H28" t="n">
-        <v>170.422369793817</v>
+        <v>170.2623697938169</v>
       </c>
       <c r="I28" t="n">
-        <v>218.3052487298999</v>
+        <v>218.1452487298998</v>
       </c>
       <c r="J28" t="n">
-        <v>406.1389893823512</v>
+        <v>405.9789893823512</v>
       </c>
       <c r="K28" t="n">
-        <v>406.1389893823512</v>
+        <v>405.9789893823512</v>
       </c>
       <c r="L28" t="n">
-        <v>406.1389893823512</v>
+        <v>405.9789893823512</v>
       </c>
       <c r="M28" t="n">
-        <v>406.1389893823512</v>
+        <v>405.9789893823512</v>
       </c>
       <c r="N28" t="n">
-        <v>406.1389893823512</v>
+        <v>405.9789893823512</v>
       </c>
       <c r="O28" t="n">
-        <v>406.1389893823512</v>
+        <v>405.9789893823512</v>
       </c>
       <c r="P28" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="Q28" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="R28" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="S28" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="T28" t="n">
-        <v>76.74567915880486</v>
+        <v>76.58567915880487</v>
       </c>
       <c r="U28" t="n">
-        <v>150.0468717970915</v>
+        <v>149.8868717970915</v>
       </c>
       <c r="V28" t="n">
-        <v>175.6182646830375</v>
+        <v>175.4582646830374</v>
       </c>
       <c r="W28" t="n">
-        <v>174.2315880782802</v>
+        <v>174.0715880782802</v>
       </c>
       <c r="X28" t="n">
-        <v>174.2315880782802</v>
+        <v>174.0715880782802</v>
       </c>
       <c r="Y28" t="n">
-        <v>174.2315880782802</v>
+        <v>174.0715880782802</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1001.128308460884</v>
+        <v>430.9831069145334</v>
       </c>
       <c r="C29" t="n">
-        <v>789.5378253871526</v>
+        <v>224.4431288913072</v>
       </c>
       <c r="D29" t="n">
-        <v>617.478072114577</v>
+        <v>224.4431288913072</v>
       </c>
       <c r="E29" t="n">
-        <v>451.4545472591541</v>
+        <v>224.4431288913072</v>
       </c>
       <c r="F29" t="n">
-        <v>284.8993667460107</v>
+        <v>224.4431288913072</v>
       </c>
       <c r="G29" t="n">
-        <v>231.626725963159</v>
+        <v>224.4431288913072</v>
       </c>
       <c r="H29" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="I29" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="J29" t="n">
-        <v>453.2291130376557</v>
+        <v>453.0691130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>1124.880904947333</v>
+        <v>1048.591171271053</v>
       </c>
       <c r="L29" t="n">
-        <v>1124.880904947333</v>
+        <v>1048.591171271053</v>
       </c>
       <c r="M29" t="n">
-        <v>1124.880904947333</v>
+        <v>1559.439999999988</v>
       </c>
       <c r="N29" t="n">
-        <v>1124.880904947333</v>
+        <v>1559.439999999988</v>
       </c>
       <c r="O29" t="n">
-        <v>1891.140904947333</v>
+        <v>2323.719999999994</v>
       </c>
       <c r="P29" t="n">
-        <v>2657.400904947332</v>
+        <v>3088</v>
       </c>
       <c r="Q29" t="n">
-        <v>3096</v>
+        <v>3088</v>
       </c>
       <c r="R29" t="n">
-        <v>3085.011516335056</v>
+        <v>3082.062021385561</v>
       </c>
       <c r="S29" t="n">
-        <v>3085.011516335056</v>
+        <v>2829.690134716549</v>
       </c>
       <c r="T29" t="n">
-        <v>3085.011516335056</v>
+        <v>2484.563284485676</v>
       </c>
       <c r="U29" t="n">
-        <v>2671.65667133646</v>
+        <v>2076.258944537584</v>
       </c>
       <c r="V29" t="n">
-        <v>2277.867758036637</v>
+        <v>1687.520536288267</v>
       </c>
       <c r="W29" t="n">
-        <v>1875.470307550832</v>
+        <v>1290.173590852967</v>
       </c>
       <c r="X29" t="n">
-        <v>1519.630071731975</v>
+        <v>939.3838600846152</v>
       </c>
       <c r="Y29" t="n">
-        <v>1245.57205892106</v>
+        <v>670.3763523242046</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>677.3276383479393</v>
+        <v>646.864608044909</v>
       </c>
       <c r="C30" t="n">
-        <v>555.0044944635764</v>
+        <v>529.5919692110512</v>
       </c>
       <c r="D30" t="n">
-        <v>445.9765279002404</v>
+        <v>425.6145076982202</v>
       </c>
       <c r="E30" t="n">
-        <v>342.2673387871973</v>
+        <v>326.9558236356822</v>
       </c>
       <c r="F30" t="n">
-        <v>241.6246697590389</v>
+        <v>231.3636596580288</v>
       </c>
       <c r="G30" t="n">
-        <v>155.019077966082</v>
+        <v>149.8085729155769</v>
       </c>
       <c r="H30" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="I30" t="n">
-        <v>84.56487796756495</v>
+        <v>89.35487796756495</v>
       </c>
       <c r="J30" t="n">
-        <v>356.5743734163872</v>
+        <v>213.3113981428639</v>
       </c>
       <c r="K30" t="n">
-        <v>545.7671895107705</v>
+        <v>645.0542142372473</v>
       </c>
       <c r="L30" t="n">
-        <v>817.1176511059707</v>
+        <v>1158.954675832447</v>
       </c>
       <c r="M30" t="n">
-        <v>1140.79819284883</v>
+        <v>1245.035217575307</v>
       </c>
       <c r="N30" t="n">
-        <v>1511.678477456398</v>
+        <v>1420.910901698822</v>
       </c>
       <c r="O30" t="n">
-        <v>1988.320929140117</v>
+        <v>1902.503353382541</v>
       </c>
       <c r="P30" t="n">
-        <v>2338.450273609624</v>
+        <v>2257.582697852048</v>
       </c>
       <c r="Q30" t="n">
-        <v>2404.701801170049</v>
+        <v>2328.784225412473</v>
       </c>
       <c r="R30" t="n">
-        <v>2094.324228147444</v>
+        <v>2023.457157440373</v>
       </c>
       <c r="S30" t="n">
-        <v>1865.471702930664</v>
+        <v>1799.655137274099</v>
       </c>
       <c r="T30" t="n">
-        <v>1698.443657256408</v>
+        <v>1637.677596650347</v>
       </c>
       <c r="U30" t="n">
-        <v>1536.615011033997</v>
+        <v>1480.899455478441</v>
       </c>
       <c r="V30" t="n">
-        <v>1360.341609830441</v>
+        <v>1309.676559325391</v>
       </c>
       <c r="W30" t="n">
-        <v>1166.025303860918</v>
+        <v>1120.410758406372</v>
       </c>
       <c r="X30" t="n">
-        <v>984.3457690675968</v>
+        <v>943.7817286635565</v>
       </c>
       <c r="Y30" t="n">
-        <v>823.3443622331177</v>
+        <v>787.8308268795823</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>233.6591829427149</v>
+        <v>253.2991829427149</v>
       </c>
       <c r="C31" t="n">
-        <v>233.6591829427149</v>
+        <v>253.2991829427149</v>
       </c>
       <c r="D31" t="n">
-        <v>233.6591829427149</v>
+        <v>253.2991829427149</v>
       </c>
       <c r="E31" t="n">
-        <v>192.2643295720517</v>
+        <v>216.9548346225567</v>
       </c>
       <c r="F31" t="n">
-        <v>192.2643295720517</v>
+        <v>216.9548346225567</v>
       </c>
       <c r="G31" t="n">
-        <v>192.2643295720517</v>
+        <v>216.9548346225567</v>
       </c>
       <c r="H31" t="n">
-        <v>203.3809147314493</v>
+        <v>233.0214197819543</v>
       </c>
       <c r="I31" t="n">
-        <v>266.1137936675322</v>
+        <v>300.7042987180372</v>
       </c>
       <c r="J31" t="n">
-        <v>468.7975343199835</v>
+        <v>508.3380393704885</v>
       </c>
       <c r="K31" t="n">
-        <v>468.7975343199835</v>
+        <v>508.3380393704885</v>
       </c>
       <c r="L31" t="n">
-        <v>468.7975343199835</v>
+        <v>327.9868998171762</v>
       </c>
       <c r="M31" t="n">
-        <v>468.7975343199835</v>
+        <v>327.9868998171762</v>
       </c>
       <c r="N31" t="n">
-        <v>468.7975343199835</v>
+        <v>327.9868998171762</v>
       </c>
       <c r="O31" t="n">
-        <v>468.7975343199835</v>
+        <v>327.9868998171762</v>
       </c>
       <c r="P31" t="n">
-        <v>468.7975343199835</v>
+        <v>327.9868998171762</v>
       </c>
       <c r="Q31" t="n">
-        <v>61.92</v>
+        <v>327.9868998171762</v>
       </c>
       <c r="R31" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="S31" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="T31" t="n">
-        <v>91.59567915880487</v>
+        <v>96.38567915880486</v>
       </c>
       <c r="U31" t="n">
-        <v>179.7468717970915</v>
+        <v>189.4868717970915</v>
       </c>
       <c r="V31" t="n">
-        <v>220.1682646830375</v>
+        <v>234.8582646830375</v>
       </c>
       <c r="W31" t="n">
-        <v>233.6591829427149</v>
+        <v>253.2991829427149</v>
       </c>
       <c r="X31" t="n">
-        <v>233.6591829427149</v>
+        <v>253.2991829427149</v>
       </c>
       <c r="Y31" t="n">
-        <v>233.6591829427149</v>
+        <v>253.2991829427149</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>810.2368518063311</v>
+        <v>800.5574491653355</v>
       </c>
       <c r="C32" t="n">
-        <v>649.1514192376503</v>
+        <v>639.4720165966547</v>
       </c>
       <c r="D32" t="n">
-        <v>527.5967164701253</v>
+        <v>517.9173138291296</v>
       </c>
       <c r="E32" t="n">
-        <v>412.078242119753</v>
+        <v>402.3988394787573</v>
       </c>
       <c r="F32" t="n">
-        <v>296.0281121116602</v>
+        <v>286.3487094706645</v>
       </c>
       <c r="G32" t="n">
-        <v>181.1216754581085</v>
+        <v>180.9616754581085</v>
       </c>
       <c r="H32" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="I32" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="J32" t="n">
-        <v>61.92</v>
+        <v>445.4962932738044</v>
       </c>
       <c r="K32" t="n">
-        <v>771.6263663478684</v>
+        <v>435.3165218277339</v>
       </c>
       <c r="L32" t="n">
-        <v>929.5566831303572</v>
+        <v>532.8183299383287</v>
       </c>
       <c r="M32" t="n">
-        <v>913.9985013121749</v>
+        <v>517.3003501403489</v>
       </c>
       <c r="N32" t="n">
-        <v>1524.111495674753</v>
+        <v>1127.453546523129</v>
       </c>
       <c r="O32" t="n">
-        <v>2290.371495674754</v>
+        <v>1891.733546523137</v>
       </c>
       <c r="P32" t="n">
-        <v>3056.631495674754</v>
+        <v>2656.013546523143</v>
       </c>
       <c r="Q32" t="n">
-        <v>3096</v>
+        <v>3088</v>
       </c>
       <c r="R32" t="n">
-        <v>3096</v>
+        <v>3088</v>
       </c>
       <c r="S32" t="n">
-        <v>2889.082658785532</v>
+        <v>2881.082658785532</v>
       </c>
       <c r="T32" t="n">
-        <v>2591.0897566502</v>
+        <v>2581.410354009205</v>
       </c>
       <c r="U32" t="n">
-        <v>2228.239962156654</v>
+        <v>2218.560559515659</v>
       </c>
       <c r="V32" t="n">
-        <v>1884.956099361883</v>
+        <v>1875.276696720887</v>
       </c>
       <c r="W32" t="n">
-        <v>1533.063699381128</v>
+        <v>1523.384296740132</v>
       </c>
       <c r="X32" t="n">
-        <v>1227.728514067322</v>
+        <v>1218.049111426326</v>
       </c>
       <c r="Y32" t="n">
-        <v>1004.175551761457</v>
+        <v>994.4961491204613</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>374.2973353176363</v>
+        <v>374.1373353176363</v>
       </c>
       <c r="C33" t="n">
-        <v>302.4792419383239</v>
+        <v>302.3192419383238</v>
       </c>
       <c r="D33" t="n">
-        <v>243.9563258800384</v>
+        <v>243.7963258800384</v>
       </c>
       <c r="E33" t="n">
-        <v>190.7521872720458</v>
+        <v>190.5921872720458</v>
       </c>
       <c r="F33" t="n">
-        <v>140.6145687489379</v>
+        <v>140.4545687489378</v>
       </c>
       <c r="G33" t="n">
-        <v>104.5140274610314</v>
+        <v>104.3540274610314</v>
       </c>
       <c r="H33" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="I33" t="n">
-        <v>88.84209566533033</v>
+        <v>88.68209566533039</v>
       </c>
       <c r="J33" t="n">
-        <v>212.7986158406293</v>
+        <v>212.6386158406293</v>
       </c>
       <c r="K33" t="n">
-        <v>689.0914319350127</v>
+        <v>401.8314319350127</v>
       </c>
       <c r="L33" t="n">
-        <v>960.4418935302127</v>
+        <v>673.1818935302128</v>
       </c>
       <c r="M33" t="n">
-        <v>1046.522435273072</v>
+        <v>759.2624352730721</v>
       </c>
       <c r="N33" t="n">
-        <v>1179.80271988064</v>
+        <v>892.5427198806404</v>
       </c>
       <c r="O33" t="n">
-        <v>1418.845171564359</v>
+        <v>1131.585171564359</v>
       </c>
       <c r="P33" t="n">
-        <v>1531.374516033866</v>
+        <v>1531.214516033866</v>
       </c>
       <c r="Q33" t="n">
-        <v>1647.126043594291</v>
+        <v>1646.966043594291</v>
       </c>
       <c r="R33" t="n">
-        <v>1387.253521076736</v>
+        <v>1387.093521076736</v>
       </c>
       <c r="S33" t="n">
-        <v>1208.906046365008</v>
+        <v>1208.746046365008</v>
       </c>
       <c r="T33" t="n">
-        <v>1092.383051195802</v>
+        <v>1092.223051195802</v>
       </c>
       <c r="U33" t="n">
-        <v>981.0594554784415</v>
+        <v>980.8994554784415</v>
       </c>
       <c r="V33" t="n">
-        <v>855.2911047799363</v>
+        <v>855.1311047799363</v>
       </c>
       <c r="W33" t="n">
-        <v>711.4798493154631</v>
+        <v>711.3198493154631</v>
       </c>
       <c r="X33" t="n">
-        <v>580.3053650271928</v>
+        <v>580.1453650271928</v>
       </c>
       <c r="Y33" t="n">
-        <v>469.8090086977642</v>
+        <v>469.6490086977641</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>479.1566123122328</v>
+        <v>478.9966123122328</v>
       </c>
       <c r="C34" t="n">
-        <v>496.2586181306686</v>
+        <v>496.0986181306686</v>
       </c>
       <c r="D34" t="n">
-        <v>500.6777622556687</v>
+        <v>500.5177622556686</v>
       </c>
       <c r="E34" t="n">
-        <v>509.6066664670817</v>
+        <v>509.4466664670816</v>
       </c>
       <c r="F34" t="n">
-        <v>525.0676390590171</v>
+        <v>524.9076390590171</v>
       </c>
       <c r="G34" t="n">
-        <v>569.5742049459024</v>
+        <v>569.4142049459024</v>
       </c>
       <c r="H34" t="n">
-        <v>630.1907901052999</v>
+        <v>630.0307901053</v>
       </c>
       <c r="I34" t="n">
-        <v>742.4236690413828</v>
+        <v>742.2636690413829</v>
       </c>
       <c r="J34" t="n">
-        <v>994.6074096938341</v>
+        <v>994.4474096938342</v>
       </c>
       <c r="K34" t="n">
-        <v>996.0718436307026</v>
+        <v>995.9118436307026</v>
       </c>
       <c r="L34" t="n">
-        <v>861.1752495319357</v>
+        <v>995.9118436307026</v>
       </c>
       <c r="M34" t="n">
-        <v>628.2140258929965</v>
+        <v>995.9118436307026</v>
       </c>
       <c r="N34" t="n">
-        <v>344.1886973357389</v>
+        <v>995.9118436307026</v>
       </c>
       <c r="O34" t="n">
-        <v>344.1886973357389</v>
+        <v>995.9118436307026</v>
       </c>
       <c r="P34" t="n">
-        <v>344.1886973357389</v>
+        <v>943.013933744191</v>
       </c>
       <c r="Q34" t="n">
-        <v>344.1886973357389</v>
+        <v>502.7722504860112</v>
       </c>
       <c r="R34" t="n">
-        <v>135.0245249523792</v>
+        <v>61.76</v>
       </c>
       <c r="S34" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="T34" t="n">
-        <v>141.0956791588049</v>
+        <v>140.9356791588049</v>
       </c>
       <c r="U34" t="n">
-        <v>278.7468717970915</v>
+        <v>278.5868717970915</v>
       </c>
       <c r="V34" t="n">
-        <v>368.6682646830375</v>
+        <v>368.5082646830375</v>
       </c>
       <c r="W34" t="n">
-        <v>431.6591829427149</v>
+        <v>431.4991829427149</v>
       </c>
       <c r="X34" t="n">
-        <v>473.7899739669084</v>
+        <v>473.6299739669084</v>
       </c>
       <c r="Y34" t="n">
-        <v>476.2992746459407</v>
+        <v>476.1392746459406</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>810.2368518063311</v>
+        <v>810.0768518063312</v>
       </c>
       <c r="C35" t="n">
-        <v>649.1514192376503</v>
+        <v>648.9914192376505</v>
       </c>
       <c r="D35" t="n">
-        <v>527.5967164701253</v>
+        <v>527.4367164701254</v>
       </c>
       <c r="E35" t="n">
-        <v>412.078242119753</v>
+        <v>411.918242119753</v>
       </c>
       <c r="F35" t="n">
-        <v>296.0281121116602</v>
+        <v>295.8681121116603</v>
       </c>
       <c r="G35" t="n">
-        <v>181.1216754581085</v>
+        <v>180.9616754581085</v>
       </c>
       <c r="H35" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="I35" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="J35" t="n">
-        <v>445.6160912536023</v>
+        <v>445.4962932738044</v>
       </c>
       <c r="K35" t="n">
-        <v>443.5577339489462</v>
+        <v>429.9783134758245</v>
       </c>
       <c r="L35" t="n">
-        <v>427.9995521307642</v>
+        <v>532.8183299383287</v>
       </c>
       <c r="M35" t="n">
-        <v>933.6624995125976</v>
+        <v>517.3003501403489</v>
       </c>
       <c r="N35" t="n">
-        <v>1131.533748543345</v>
+        <v>1127.453546523129</v>
       </c>
       <c r="O35" t="n">
-        <v>1897.793748543345</v>
+        <v>1891.733546523137</v>
       </c>
       <c r="P35" t="n">
-        <v>2664.053748543345</v>
+        <v>2656.013546523143</v>
       </c>
       <c r="Q35" t="n">
-        <v>3096</v>
+        <v>3088</v>
       </c>
       <c r="R35" t="n">
-        <v>3096</v>
+        <v>3088.000000000023</v>
       </c>
       <c r="S35" t="n">
-        <v>2890.762061426527</v>
+        <v>2881.082658785555</v>
       </c>
       <c r="T35" t="n">
-        <v>2591.0897566502</v>
+        <v>2581.410354009228</v>
       </c>
       <c r="U35" t="n">
-        <v>2228.239962156654</v>
+        <v>2218.560559515682</v>
       </c>
       <c r="V35" t="n">
-        <v>1884.956099361883</v>
+        <v>1875.27669672091</v>
       </c>
       <c r="W35" t="n">
-        <v>1533.063699381128</v>
+        <v>1523.384296740155</v>
       </c>
       <c r="X35" t="n">
-        <v>1227.728514067322</v>
+        <v>1218.04911142635</v>
       </c>
       <c r="Y35" t="n">
-        <v>1004.175551761457</v>
+        <v>994.4961491204845</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>374.2973353176363</v>
+        <v>374.1373353176363</v>
       </c>
       <c r="C36" t="n">
-        <v>302.4792419383239</v>
+        <v>302.3192419383238</v>
       </c>
       <c r="D36" t="n">
-        <v>243.9563258800384</v>
+        <v>243.7963258800384</v>
       </c>
       <c r="E36" t="n">
-        <v>190.7521872720458</v>
+        <v>190.5921872720458</v>
       </c>
       <c r="F36" t="n">
-        <v>140.6145687489379</v>
+        <v>140.4545687489378</v>
       </c>
       <c r="G36" t="n">
-        <v>104.5140274610314</v>
+        <v>104.3540274610314</v>
       </c>
       <c r="H36" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="I36" t="n">
-        <v>88.84209566533025</v>
+        <v>88.68209566533039</v>
       </c>
       <c r="J36" t="n">
-        <v>212.7986158406292</v>
+        <v>212.6386158406293</v>
       </c>
       <c r="K36" t="n">
-        <v>401.9914319350126</v>
+        <v>401.8314319350127</v>
       </c>
       <c r="L36" t="n">
-        <v>673.3418935302127</v>
+        <v>673.1818935302128</v>
       </c>
       <c r="M36" t="n">
-        <v>759.422435273072</v>
+        <v>759.2624352730721</v>
       </c>
       <c r="N36" t="n">
-        <v>892.7027198806403</v>
+        <v>892.5427198806404</v>
       </c>
       <c r="O36" t="n">
-        <v>1131.745171564359</v>
+        <v>1131.585171564359</v>
       </c>
       <c r="P36" t="n">
-        <v>1531.374516033866</v>
+        <v>1531.214516033866</v>
       </c>
       <c r="Q36" t="n">
-        <v>1647.126043594291</v>
+        <v>1646.966043594291</v>
       </c>
       <c r="R36" t="n">
-        <v>1387.253521076736</v>
+        <v>1387.093521076736</v>
       </c>
       <c r="S36" t="n">
-        <v>1208.906046365008</v>
+        <v>1208.746046365008</v>
       </c>
       <c r="T36" t="n">
-        <v>1092.383051195802</v>
+        <v>1092.223051195802</v>
       </c>
       <c r="U36" t="n">
-        <v>981.0594554784415</v>
+        <v>980.8994554784415</v>
       </c>
       <c r="V36" t="n">
-        <v>855.2911047799363</v>
+        <v>855.1311047799363</v>
       </c>
       <c r="W36" t="n">
-        <v>711.4798493154631</v>
+        <v>711.3198493154631</v>
       </c>
       <c r="X36" t="n">
-        <v>580.3053650271928</v>
+        <v>580.1453650271928</v>
       </c>
       <c r="Y36" t="n">
-        <v>469.8090086977642</v>
+        <v>469.6490086977641</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>479.1566123122328</v>
+        <v>478.9966123122328</v>
       </c>
       <c r="C37" t="n">
-        <v>496.2586181306686</v>
+        <v>496.0986181306686</v>
       </c>
       <c r="D37" t="n">
-        <v>500.6777622556687</v>
+        <v>500.5177622556686</v>
       </c>
       <c r="E37" t="n">
-        <v>509.6066664670817</v>
+        <v>509.4466664670816</v>
       </c>
       <c r="F37" t="n">
-        <v>525.0676390590171</v>
+        <v>524.9076390590171</v>
       </c>
       <c r="G37" t="n">
-        <v>569.5742049459024</v>
+        <v>569.4142049459024</v>
       </c>
       <c r="H37" t="n">
-        <v>630.1907901052999</v>
+        <v>630.0307901053</v>
       </c>
       <c r="I37" t="n">
-        <v>742.4236690413828</v>
+        <v>742.2636690413829</v>
       </c>
       <c r="J37" t="n">
-        <v>994.6074096938341</v>
+        <v>994.4474096938342</v>
       </c>
       <c r="K37" t="n">
-        <v>996.0718436307026</v>
+        <v>995.9118436307026</v>
       </c>
       <c r="L37" t="n">
-        <v>996.0718436307026</v>
+        <v>995.9118436307026</v>
       </c>
       <c r="M37" t="n">
-        <v>996.0718436307026</v>
+        <v>995.9118436307026</v>
       </c>
       <c r="N37" t="n">
-        <v>712.0465150734451</v>
+        <v>995.9118436307026</v>
       </c>
       <c r="O37" t="n">
-        <v>712.0465150734451</v>
+        <v>995.9118436307026</v>
       </c>
       <c r="P37" t="n">
-        <v>712.0465150734451</v>
+        <v>995.9118436307026</v>
       </c>
       <c r="Q37" t="n">
-        <v>502.9322504860112</v>
+        <v>555.6701603725228</v>
       </c>
       <c r="R37" t="n">
-        <v>61.92</v>
+        <v>114.6579098865116</v>
       </c>
       <c r="S37" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="T37" t="n">
-        <v>141.0956791588049</v>
+        <v>140.9356791588049</v>
       </c>
       <c r="U37" t="n">
-        <v>278.7468717970915</v>
+        <v>278.5868717970915</v>
       </c>
       <c r="V37" t="n">
-        <v>368.6682646830375</v>
+        <v>368.5082646830375</v>
       </c>
       <c r="W37" t="n">
-        <v>431.6591829427149</v>
+        <v>431.4991829427149</v>
       </c>
       <c r="X37" t="n">
-        <v>473.7899739669084</v>
+        <v>473.6299739669084</v>
       </c>
       <c r="Y37" t="n">
-        <v>476.2992746459407</v>
+        <v>476.1392746459406</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>810.2368518063311</v>
+        <v>810.0768518063312</v>
       </c>
       <c r="C38" t="n">
-        <v>649.1514192376503</v>
+        <v>648.9914192376505</v>
       </c>
       <c r="D38" t="n">
-        <v>527.5967164701253</v>
+        <v>527.4367164701254</v>
       </c>
       <c r="E38" t="n">
-        <v>412.078242119753</v>
+        <v>411.918242119753</v>
       </c>
       <c r="F38" t="n">
-        <v>296.0281121116602</v>
+        <v>295.8681121116603</v>
       </c>
       <c r="G38" t="n">
-        <v>181.1216754581085</v>
+        <v>180.9616754581085</v>
       </c>
       <c r="H38" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="I38" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="J38" t="n">
-        <v>445.6160912536023</v>
+        <v>445.4962932738044</v>
       </c>
       <c r="K38" t="n">
-        <v>430.0579094354204</v>
+        <v>647.4481483651443</v>
       </c>
       <c r="L38" t="n">
-        <v>427.9995521307642</v>
+        <v>637.2683769190738</v>
       </c>
       <c r="M38" t="n">
-        <v>933.6624995125976</v>
+        <v>1142.971526321109</v>
       </c>
       <c r="N38" t="n">
-        <v>1543.775493875176</v>
+        <v>1127.453546523129</v>
       </c>
       <c r="O38" t="n">
-        <v>2310.035493875176</v>
+        <v>1891.733546523137</v>
       </c>
       <c r="P38" t="n">
-        <v>3076.295493875176</v>
+        <v>2656.013546523143</v>
       </c>
       <c r="Q38" t="n">
-        <v>3096</v>
+        <v>3088</v>
       </c>
       <c r="R38" t="n">
-        <v>3096</v>
+        <v>3088</v>
       </c>
       <c r="S38" t="n">
-        <v>2889.082658785532</v>
+        <v>2881.082658785532</v>
       </c>
       <c r="T38" t="n">
-        <v>2589.410354009205</v>
+        <v>2581.410354009205</v>
       </c>
       <c r="U38" t="n">
-        <v>2226.560559515659</v>
+        <v>2218.560559515659</v>
       </c>
       <c r="V38" t="n">
-        <v>1884.956099361883</v>
+        <v>1875.276696720887</v>
       </c>
       <c r="W38" t="n">
-        <v>1533.063699381128</v>
+        <v>1523.384296740132</v>
       </c>
       <c r="X38" t="n">
-        <v>1227.728514067322</v>
+        <v>1218.049111426326</v>
       </c>
       <c r="Y38" t="n">
-        <v>1004.175551761457</v>
+        <v>994.4961491204613</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>374.2973353176363</v>
+        <v>374.1373353176363</v>
       </c>
       <c r="C39" t="n">
-        <v>302.4792419383239</v>
+        <v>302.3192419383238</v>
       </c>
       <c r="D39" t="n">
-        <v>243.9563258800384</v>
+        <v>243.7963258800384</v>
       </c>
       <c r="E39" t="n">
-        <v>190.7521872720458</v>
+        <v>190.5921872720458</v>
       </c>
       <c r="F39" t="n">
-        <v>140.6145687489379</v>
+        <v>140.4545687489378</v>
       </c>
       <c r="G39" t="n">
-        <v>104.5140274610314</v>
+        <v>104.3540274610314</v>
       </c>
       <c r="H39" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="I39" t="n">
-        <v>134.0648779675649</v>
+        <v>88.68209566533051</v>
       </c>
       <c r="J39" t="n">
-        <v>258.0213981428639</v>
+        <v>212.6386158406295</v>
       </c>
       <c r="K39" t="n">
-        <v>734.3142142372473</v>
+        <v>401.8314319350129</v>
       </c>
       <c r="L39" t="n">
-        <v>1005.664675832447</v>
+        <v>673.181893530213</v>
       </c>
       <c r="M39" t="n">
-        <v>1091.745217575306</v>
+        <v>759.2624352730722</v>
       </c>
       <c r="N39" t="n">
-        <v>1225.025502182875</v>
+        <v>1179.64271988064</v>
       </c>
       <c r="O39" t="n">
-        <v>1464.067953866594</v>
+        <v>1418.685171564359</v>
       </c>
       <c r="P39" t="n">
-        <v>1576.5972983361</v>
+        <v>1531.214516033866</v>
       </c>
       <c r="Q39" t="n">
-        <v>1647.126043594291</v>
+        <v>1646.966043594291</v>
       </c>
       <c r="R39" t="n">
-        <v>1387.253521076736</v>
+        <v>1387.093521076736</v>
       </c>
       <c r="S39" t="n">
-        <v>1208.906046365008</v>
+        <v>1208.746046365008</v>
       </c>
       <c r="T39" t="n">
-        <v>1092.383051195802</v>
+        <v>1092.223051195802</v>
       </c>
       <c r="U39" t="n">
-        <v>981.0594554784415</v>
+        <v>980.8994554784415</v>
       </c>
       <c r="V39" t="n">
-        <v>855.2911047799363</v>
+        <v>855.1311047799363</v>
       </c>
       <c r="W39" t="n">
-        <v>711.4798493154631</v>
+        <v>711.3198493154631</v>
       </c>
       <c r="X39" t="n">
-        <v>580.3053650271928</v>
+        <v>580.1453650271928</v>
       </c>
       <c r="Y39" t="n">
-        <v>469.8090086977642</v>
+        <v>469.6490086977641</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>479.1566123122328</v>
+        <v>478.9966123122328</v>
       </c>
       <c r="C40" t="n">
-        <v>496.2586181306686</v>
+        <v>496.0986181306686</v>
       </c>
       <c r="D40" t="n">
-        <v>500.6777622556687</v>
+        <v>500.5177622556686</v>
       </c>
       <c r="E40" t="n">
-        <v>509.6066664670817</v>
+        <v>509.4466664670816</v>
       </c>
       <c r="F40" t="n">
-        <v>525.0676390590171</v>
+        <v>524.9076390590171</v>
       </c>
       <c r="G40" t="n">
-        <v>569.5742049459024</v>
+        <v>569.4142049459024</v>
       </c>
       <c r="H40" t="n">
-        <v>630.1907901052999</v>
+        <v>630.0307901053</v>
       </c>
       <c r="I40" t="n">
-        <v>742.4236690413828</v>
+        <v>742.2636690413829</v>
       </c>
       <c r="J40" t="n">
-        <v>994.6074096938341</v>
+        <v>994.4474096938342</v>
       </c>
       <c r="K40" t="n">
-        <v>996.0718436307026</v>
+        <v>995.9118436307026</v>
       </c>
       <c r="L40" t="n">
-        <v>996.0718436307026</v>
+        <v>995.9118436307026</v>
       </c>
       <c r="M40" t="n">
-        <v>996.0718436307026</v>
+        <v>995.9118436307026</v>
       </c>
       <c r="N40" t="n">
-        <v>996.0718436307026</v>
+        <v>995.9118436307026</v>
       </c>
       <c r="O40" t="n">
-        <v>996.0718436307026</v>
+        <v>903.4642058119955</v>
       </c>
       <c r="P40" t="n">
-        <v>943.173933744191</v>
+        <v>502.0016832581798</v>
       </c>
       <c r="Q40" t="n">
-        <v>502.9322504860112</v>
+        <v>61.76</v>
       </c>
       <c r="R40" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="S40" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="T40" t="n">
-        <v>141.0956791588049</v>
+        <v>140.9356791588049</v>
       </c>
       <c r="U40" t="n">
-        <v>278.7468717970915</v>
+        <v>278.5868717970915</v>
       </c>
       <c r="V40" t="n">
-        <v>368.6682646830375</v>
+        <v>368.5082646830375</v>
       </c>
       <c r="W40" t="n">
-        <v>431.6591829427149</v>
+        <v>431.4991829427149</v>
       </c>
       <c r="X40" t="n">
-        <v>473.7899739669084</v>
+        <v>473.6299739669084</v>
       </c>
       <c r="Y40" t="n">
-        <v>476.2992746459407</v>
+        <v>476.1392746459406</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>824.2380042470395</v>
+        <v>831.205944797548</v>
       </c>
       <c r="C41" t="n">
-        <v>581.334389860177</v>
+        <v>589.3124314207864</v>
       </c>
       <c r="D41" t="n">
-        <v>459.6644757480238</v>
+        <v>589.3124314207864</v>
       </c>
       <c r="E41" t="n">
-        <v>459.6644757480238</v>
+        <v>392.9858762623332</v>
       </c>
       <c r="F41" t="n">
-        <v>459.6644757480238</v>
+        <v>392.9858762623332</v>
       </c>
       <c r="G41" t="n">
-        <v>262.9398572762903</v>
+        <v>261.7697562661893</v>
       </c>
       <c r="H41" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="I41" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="J41" t="n">
-        <v>453.2291130376557</v>
+        <v>453.0691130376557</v>
       </c>
       <c r="K41" t="n">
-        <v>1162.935479385524</v>
+        <v>453.0691130376557</v>
       </c>
       <c r="L41" t="n">
-        <v>1929.195479385524</v>
+        <v>1120.840904947319</v>
       </c>
       <c r="M41" t="n">
-        <v>2440.044308114459</v>
+        <v>1120.840904947319</v>
       </c>
       <c r="N41" t="n">
-        <v>3053.264627889223</v>
+        <v>1120.840904947319</v>
       </c>
       <c r="O41" t="n">
-        <v>3053.264627889223</v>
+        <v>1885.120904947326</v>
       </c>
       <c r="P41" t="n">
-        <v>3053.264627889223</v>
+        <v>2649.400904947332</v>
       </c>
       <c r="Q41" t="n">
-        <v>3096</v>
+        <v>3088</v>
       </c>
       <c r="R41" t="n">
-        <v>3096</v>
+        <v>3046.708486032026</v>
       </c>
       <c r="S41" t="n">
-        <v>3096</v>
+        <v>2758.983064009477</v>
       </c>
       <c r="T41" t="n">
-        <v>3096</v>
+        <v>2378.502678425069</v>
       </c>
       <c r="U41" t="n">
-        <v>2651.332023688272</v>
+        <v>2378.502678425069</v>
       </c>
       <c r="V41" t="n">
-        <v>2226.229979075319</v>
+        <v>1954.410734822216</v>
       </c>
       <c r="W41" t="n">
-        <v>1792.519397276382</v>
+        <v>1521.710254033381</v>
       </c>
       <c r="X41" t="n">
-        <v>1405.366030144394</v>
+        <v>1135.566987911494</v>
       </c>
       <c r="Y41" t="n">
-        <v>1099.994886020347</v>
+        <v>831.205944797548</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>873.4148968240489</v>
+        <v>866.184189753342</v>
       </c>
       <c r="C42" t="n">
-        <v>719.7786216265547</v>
+        <v>713.5580155659487</v>
       </c>
       <c r="D42" t="n">
-        <v>579.4375237500874</v>
+        <v>574.2270186995825</v>
       </c>
       <c r="E42" t="n">
-        <v>444.415203323913</v>
+        <v>440.214799283509</v>
       </c>
       <c r="F42" t="n">
-        <v>312.4594029826233</v>
+        <v>309.2690999523202</v>
       </c>
       <c r="G42" t="n">
-        <v>194.540679876535</v>
+        <v>192.360477856333</v>
       </c>
       <c r="H42" t="n">
-        <v>70.12847059732175</v>
+        <v>68.95836958722074</v>
       </c>
       <c r="I42" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="J42" t="n">
-        <v>392.786520175299</v>
+        <v>393.6165201752989</v>
       </c>
       <c r="K42" t="n">
-        <v>788.8893362696824</v>
+        <v>790.7093362696824</v>
       </c>
       <c r="L42" t="n">
-        <v>1196.041406026769</v>
+        <v>1269.959797864883</v>
       </c>
       <c r="M42" t="n">
-        <v>1489.031947769628</v>
+        <v>1563.940339607742</v>
       </c>
       <c r="N42" t="n">
-        <v>1829.222232377197</v>
+        <v>1905.12062421531</v>
       </c>
       <c r="O42" t="n">
-        <v>2275.174684060916</v>
+        <v>2352.063075899029</v>
       </c>
       <c r="P42" t="n">
-        <v>2594.614028530422</v>
+        <v>2605.705049113612</v>
       </c>
       <c r="Q42" t="n">
-        <v>2630.175556090847</v>
+        <v>2642.256576674038</v>
       </c>
       <c r="R42" t="n">
-        <v>2288.48485175511</v>
+        <v>2525.605021977088</v>
       </c>
       <c r="S42" t="n">
-        <v>2055.121443316038</v>
+        <v>2266.449466457279</v>
       </c>
       <c r="T42" t="n">
-        <v>1856.78026632865</v>
+        <v>2069.118390479992</v>
       </c>
       <c r="U42" t="n">
-        <v>1663.638488793108</v>
+        <v>1876.986713954551</v>
       </c>
       <c r="V42" t="n">
-        <v>1456.051956276421</v>
+        <v>1670.410282447965</v>
       </c>
       <c r="W42" t="n">
-        <v>1456.051956276421</v>
+        <v>1445.790946175411</v>
       </c>
       <c r="X42" t="n">
-        <v>1243.059290169969</v>
+        <v>1233.80838107906</v>
       </c>
       <c r="Y42" t="n">
-        <v>1050.744752022359</v>
+        <v>1042.503943941551</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>81.89083444607942</v>
+        <v>80.74554808876397</v>
       </c>
       <c r="C43" t="n">
-        <v>81.89083444607942</v>
+        <v>80.74554808876397</v>
       </c>
       <c r="D43" t="n">
-        <v>81.89083444607942</v>
+        <v>80.74554808876397</v>
       </c>
       <c r="E43" t="n">
-        <v>81.89083444607942</v>
+        <v>80.74554808876397</v>
       </c>
       <c r="F43" t="n">
-        <v>81.89083444607942</v>
+        <v>80.74554808876397</v>
       </c>
       <c r="G43" t="n">
-        <v>81.89083444607942</v>
+        <v>80.74554808876397</v>
       </c>
       <c r="H43" t="n">
-        <v>61.92</v>
+        <v>61.78481465278557</v>
       </c>
       <c r="I43" t="n">
-        <v>93.96287893608292</v>
+        <v>61.78481465278557</v>
       </c>
       <c r="J43" t="n">
-        <v>93.96287893608292</v>
+        <v>61.78481465278557</v>
       </c>
       <c r="K43" t="n">
-        <v>93.96287893608292</v>
+        <v>61.78481465278557</v>
       </c>
       <c r="L43" t="n">
-        <v>93.96287893608292</v>
+        <v>61.78481465278557</v>
       </c>
       <c r="M43" t="n">
-        <v>93.96287893608292</v>
+        <v>61.78481465278557</v>
       </c>
       <c r="N43" t="n">
-        <v>93.96287893608292</v>
+        <v>61.78481465278557</v>
       </c>
       <c r="O43" t="n">
-        <v>93.96287893608292</v>
+        <v>61.78481465278557</v>
       </c>
       <c r="P43" t="n">
-        <v>93.96287893608292</v>
+        <v>61.78481465278557</v>
       </c>
       <c r="Q43" t="n">
-        <v>93.96287893608292</v>
+        <v>61.78481465278557</v>
       </c>
       <c r="R43" t="n">
-        <v>93.96287893608292</v>
+        <v>61.78481465278557</v>
       </c>
       <c r="S43" t="n">
-        <v>93.96287893608292</v>
+        <v>61.78481465278557</v>
       </c>
       <c r="T43" t="n">
-        <v>92.92796327319634</v>
+        <v>61.76</v>
       </c>
       <c r="U43" t="n">
-        <v>99.43912721245285</v>
+        <v>97.28373984503638</v>
       </c>
       <c r="V43" t="n">
-        <v>99.43912721245285</v>
+        <v>97.28373984503638</v>
       </c>
       <c r="W43" t="n">
-        <v>81.89083444607942</v>
+        <v>80.74554808876397</v>
       </c>
       <c r="X43" t="n">
-        <v>81.89083444607942</v>
+        <v>80.74554808876397</v>
       </c>
       <c r="Y43" t="n">
-        <v>81.89083444607942</v>
+        <v>80.74554808876397</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1311.492031314396</v>
+        <v>310.5874300402523</v>
       </c>
       <c r="C44" t="n">
-        <v>1027.174275513392</v>
+        <v>310.5874300402523</v>
       </c>
       <c r="D44" t="n">
-        <v>782.3872495135433</v>
+        <v>61.76</v>
       </c>
       <c r="E44" t="n">
-        <v>543.6364519308478</v>
+        <v>61.76</v>
       </c>
       <c r="F44" t="n">
-        <v>304.3539986904318</v>
+        <v>61.76</v>
       </c>
       <c r="G44" t="n">
-        <v>304.3539986904318</v>
+        <v>61.76</v>
       </c>
       <c r="H44" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="I44" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="J44" t="n">
-        <v>61.92</v>
+        <v>453.0691130376557</v>
       </c>
       <c r="K44" t="n">
-        <v>771.6263663478684</v>
+        <v>453.0691130376557</v>
       </c>
       <c r="L44" t="n">
-        <v>1124.880904947333</v>
+        <v>761.0517564436278</v>
       </c>
       <c r="M44" t="n">
-        <v>1124.880904947333</v>
+        <v>1271.900585172563</v>
       </c>
       <c r="N44" t="n">
-        <v>1124.880904947333</v>
+        <v>1885.120904947326</v>
       </c>
       <c r="O44" t="n">
-        <v>1891.140904947333</v>
+        <v>1885.120904947326</v>
       </c>
       <c r="P44" t="n">
-        <v>2657.400904947332</v>
+        <v>2649.400904947332</v>
       </c>
       <c r="Q44" t="n">
-        <v>3096</v>
+        <v>3088</v>
       </c>
       <c r="R44" t="n">
-        <v>3012.284243607784</v>
+        <v>3088</v>
       </c>
       <c r="S44" t="n">
-        <v>3012.284243607784</v>
+        <v>3088</v>
       </c>
       <c r="T44" t="n">
-        <v>2610.875620605549</v>
+        <v>2661.054967950945</v>
       </c>
       <c r="U44" t="n">
-        <v>2124.793502879679</v>
+        <v>2170.932446184672</v>
       </c>
       <c r="V44" t="n">
-        <v>1658.277316852584</v>
+        <v>1700.375856117173</v>
       </c>
       <c r="W44" t="n">
-        <v>1658.277316852584</v>
+        <v>1221.21072886369</v>
       </c>
       <c r="X44" t="n">
-        <v>1658.277316852584</v>
+        <v>788.6028162771572</v>
       </c>
       <c r="Y44" t="n">
-        <v>1311.492031314396</v>
+        <v>437.7771266985649</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>989.9439449676078</v>
+        <v>672.401048380462</v>
       </c>
       <c r="C45" t="n">
-        <v>794.8935283559721</v>
+        <v>473.3102277284223</v>
       </c>
       <c r="D45" t="n">
-        <v>613.1382890653633</v>
+        <v>473.3102277284223</v>
       </c>
       <c r="E45" t="n">
-        <v>436.7018272250475</v>
+        <v>292.8333618477025</v>
       </c>
       <c r="F45" t="n">
-        <v>436.7018272250475</v>
+        <v>115.4230160518672</v>
       </c>
       <c r="G45" t="n">
-        <v>277.3689627048179</v>
+        <v>115.4230160518672</v>
       </c>
       <c r="H45" t="n">
-        <v>111.5426120114632</v>
+        <v>115.4230160518672</v>
       </c>
       <c r="I45" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="J45" t="n">
-        <v>352.196520175299</v>
+        <v>348.076520175299</v>
       </c>
       <c r="K45" t="n">
-        <v>707.7093362696824</v>
+        <v>699.6293362696824</v>
       </c>
       <c r="L45" t="n">
-        <v>1011.563634924869</v>
+        <v>970.9797978648826</v>
       </c>
       <c r="M45" t="n">
-        <v>1263.964176667729</v>
+        <v>1164.073761677799</v>
       </c>
       <c r="N45" t="n">
-        <v>1563.564461275297</v>
+        <v>1459.714046285367</v>
       </c>
       <c r="O45" t="n">
-        <v>1968.926912959016</v>
+        <v>1861.116497969086</v>
       </c>
       <c r="P45" t="n">
-        <v>2247.776257428523</v>
+        <v>2136.005842438592</v>
       </c>
       <c r="Q45" t="n">
-        <v>2247.776257428523</v>
+        <v>2126.834867599724</v>
       </c>
       <c r="R45" t="n">
-        <v>2247.776257428523</v>
+        <v>2126.834867599724</v>
       </c>
       <c r="S45" t="n">
-        <v>1966.835424382311</v>
+        <v>2126.834867599724</v>
       </c>
       <c r="T45" t="n">
-        <v>1727.080105980782</v>
+        <v>1883.039145157791</v>
       </c>
       <c r="U45" t="n">
-        <v>1727.080105980782</v>
+        <v>1644.442822167703</v>
       </c>
       <c r="V45" t="n">
-        <v>1478.079432049953</v>
+        <v>1391.401744196471</v>
       </c>
       <c r="W45" t="n">
-        <v>1478.079432049953</v>
+        <v>1391.401744196471</v>
       </c>
       <c r="X45" t="n">
-        <v>1223.67262452936</v>
+        <v>1132.954532635473</v>
       </c>
       <c r="Y45" t="n">
-        <v>989.9439449676078</v>
+        <v>895.1854490333172</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>61.92</v>
+        <v>74.52106628294774</v>
       </c>
       <c r="C46" t="n">
-        <v>61.92</v>
+        <v>74.52106628294774</v>
       </c>
       <c r="D46" t="n">
-        <v>61.92</v>
+        <v>74.52106628294774</v>
       </c>
       <c r="E46" t="n">
-        <v>61.92</v>
+        <v>74.52106628294774</v>
       </c>
       <c r="F46" t="n">
-        <v>61.92</v>
+        <v>74.52106628294774</v>
       </c>
       <c r="G46" t="n">
-        <v>61.92</v>
+        <v>74.52106628294774</v>
       </c>
       <c r="H46" t="n">
-        <v>61.92</v>
+        <v>74.52106628294774</v>
       </c>
       <c r="I46" t="n">
-        <v>61.92</v>
+        <v>61.76</v>
       </c>
       <c r="J46" t="n">
-        <v>61.92</v>
+        <v>189.2037406524513</v>
       </c>
       <c r="K46" t="n">
-        <v>61.92</v>
+        <v>189.2037406524513</v>
       </c>
       <c r="L46" t="n">
-        <v>61.92</v>
+        <v>189.2037406524513</v>
       </c>
       <c r="M46" t="n">
-        <v>61.92</v>
+        <v>189.2037406524513</v>
       </c>
       <c r="N46" t="n">
-        <v>61.92</v>
+        <v>189.2037406524513</v>
       </c>
       <c r="O46" t="n">
-        <v>61.92</v>
+        <v>189.2037406524513</v>
       </c>
       <c r="P46" t="n">
-        <v>61.92</v>
+        <v>189.2037406524513</v>
       </c>
       <c r="Q46" t="n">
-        <v>61.92</v>
+        <v>189.2037406524513</v>
       </c>
       <c r="R46" t="n">
-        <v>61.92</v>
+        <v>189.2037406524513</v>
       </c>
       <c r="S46" t="n">
-        <v>61.92</v>
+        <v>189.2037406524513</v>
       </c>
       <c r="T46" t="n">
-        <v>61.92</v>
+        <v>142.7142795350193</v>
       </c>
       <c r="U46" t="n">
-        <v>61.92</v>
+        <v>152.9829386981107</v>
       </c>
       <c r="V46" t="n">
-        <v>61.92</v>
+        <v>137.5239045038666</v>
       </c>
       <c r="W46" t="n">
-        <v>61.92</v>
+        <v>74.52106628294774</v>
       </c>
       <c r="X46" t="n">
-        <v>61.92</v>
+        <v>74.52106628294774</v>
       </c>
       <c r="Y46" t="n">
-        <v>61.92</v>
+        <v>74.52106628294774</v>
       </c>
     </row>
   </sheetData>
@@ -7967,22 +7967,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K2" t="n">
-        <v>716.8751175230994</v>
+        <v>306.2599628088302</v>
       </c>
       <c r="L2" t="n">
-        <v>783.0093003025929</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>683.049975609493</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N2" t="n">
         <v>477.2489580698352</v>
       </c>
       <c r="O2" t="n">
-        <v>70.24786957409242</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>815.2870600406815</v>
+        <v>814.2870600406815</v>
       </c>
       <c r="Q2" t="n">
         <v>615.8520732695737</v>
@@ -8201,25 +8201,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>51.26150624509023</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K5" t="n">
-        <v>387.7154961339341</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L5" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>544.2621276423173</v>
+        <v>846.6448114931339</v>
       </c>
       <c r="N5" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O5" t="n">
         <v>885.2478695740924</v>
       </c>
       <c r="P5" t="n">
-        <v>815.2870600406815</v>
+        <v>0.2870600406814674</v>
       </c>
       <c r="Q5" t="n">
         <v>615.8520732695737</v>
@@ -8444,16 +8444,16 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L8" t="n">
-        <v>815</v>
+        <v>405.788230361752</v>
       </c>
       <c r="M8" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N8" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O8" t="n">
-        <v>372.6305534249099</v>
+        <v>885.2478695740924</v>
       </c>
       <c r="P8" t="n">
         <v>0.2870600406814674</v>
@@ -8681,7 +8681,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L11" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
@@ -8690,13 +8690,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O11" t="n">
-        <v>234.7583464536658</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2870600406814136</v>
+        <v>536.7681479781663</v>
       </c>
       <c r="Q11" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8915,16 +8915,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N14" t="n">
-        <v>1096.663422488788</v>
+        <v>519.1534283342882</v>
       </c>
       <c r="O14" t="n">
         <v>885.2478695740924</v>
@@ -8933,7 +8933,7 @@
         <v>815.2870600406815</v>
       </c>
       <c r="Q14" t="n">
-        <v>239.2082787301582</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9152,25 +9152,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>683.627251010917</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>885.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P17" t="n">
         <v>815.2870600406815</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>337.3331612070587</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,25 +9386,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>814.9999999999999</v>
+        <v>242.7706698795373</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O20" t="n">
-        <v>186.9906878526441</v>
+        <v>885.2478695740924</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2870600406814136</v>
+        <v>815.2870600406815</v>
       </c>
       <c r="Q20" t="n">
         <v>615.8520732695737</v>
@@ -9623,7 +9623,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>430.3047365861567</v>
+        <v>53.6609420467413</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -9638,7 +9638,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>508.6040750346768</v>
+        <v>885.2478695740924</v>
       </c>
       <c r="P23" t="n">
         <v>815.2870600406815</v>
@@ -9860,25 +9860,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>614.8138483540246</v>
+        <v>772</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
-        <v>70.24786957409245</v>
+        <v>381.3414487720507</v>
       </c>
       <c r="P26" t="n">
-        <v>774.2870600407268</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10100,25 +10100,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>678.4361534441181</v>
+        <v>601.5374325589873</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
         <v>477.2489580698352</v>
       </c>
       <c r="O29" t="n">
-        <v>844.2478695740924</v>
+        <v>842.2478695740988</v>
       </c>
       <c r="P29" t="n">
-        <v>774.2870600406815</v>
+        <v>772.2870600406873</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,13 +10334,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>50.44560624509029</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>159.5255725075645</v>
+        <v>111.8895900294889</v>
       </c>
       <c r="M32" t="n">
         <v>544.2621276423173</v>
@@ -10349,13 +10349,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O32" t="n">
-        <v>844.2478695740924</v>
+        <v>842.2478695740997</v>
       </c>
       <c r="P32" t="n">
-        <v>774.2870600406815</v>
+        <v>772.2870600406882</v>
       </c>
       <c r="Q32" t="n">
-        <v>227.200103609479</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10577,19 +10577,19 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>111.8895900295055</v>
       </c>
       <c r="M35" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N35" t="n">
-        <v>688.5440946102754</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O35" t="n">
-        <v>844.2478695740924</v>
+        <v>842.2478695740997</v>
       </c>
       <c r="P35" t="n">
-        <v>774.2870600406815</v>
+        <v>772.2870600406882</v>
       </c>
       <c r="Q35" t="n">
         <v>615.8520732695737</v>
@@ -10811,7 +10811,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>215.2951365404266</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -10820,16 +10820,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O38" t="n">
-        <v>844.2478695740924</v>
+        <v>842.2478695740997</v>
       </c>
       <c r="P38" t="n">
-        <v>774.2870600406815</v>
+        <v>772.2870600406882</v>
       </c>
       <c r="Q38" t="n">
-        <v>207.7327453910612</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11048,25 +11048,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>774</v>
+        <v>674.5169615249122</v>
       </c>
       <c r="M41" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N41" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O41" t="n">
-        <v>70.24786957409245</v>
+        <v>842.2478695740997</v>
       </c>
       <c r="P41" t="n">
-        <v>0.2870600406814136</v>
+        <v>772.2870600406882</v>
       </c>
       <c r="Q41" t="n">
-        <v>215.9897268636242</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,25 +11282,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>356.8227662620851</v>
+        <v>311.0935791979517</v>
       </c>
       <c r="M44" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O44" t="n">
-        <v>844.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P44" t="n">
-        <v>774.2870600406815</v>
+        <v>772.2870600406882</v>
       </c>
       <c r="Q44" t="n">
         <v>615.8520732695737</v>
@@ -22700,7 +22700,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>5.662449696442479</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -23232,16 +23232,16 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23274,16 +23274,16 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>269.8481678023229</v>
+        <v>57.40845813745597</v>
       </c>
       <c r="T11" t="n">
-        <v>361.6755817285639</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>146.9046579119932</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -23381,13 +23381,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>62.11380033707866</v>
       </c>
       <c r="C13" t="n">
         <v>47.72524664804467</v>
       </c>
       <c r="D13" t="n">
-        <v>42.88619991134806</v>
+        <v>60.53621805555548</v>
       </c>
       <c r="E13" t="n">
         <v>55.98090483695654</v>
@@ -23411,7 +23411,7 @@
         <v>63.52077380114304</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>198.5476281577792</v>
       </c>
       <c r="M13" t="n">
         <v>295.6316114025499</v>
@@ -23429,7 +23429,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S13" t="n">
         <v>137.3734797028554</v>
@@ -23450,7 +23450,7 @@
         <v>22.44364543010755</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>62.46535284946236</v>
       </c>
     </row>
     <row r="14">
@@ -23654,13 +23654,13 @@
         <v>269.6316114025499</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>320.1850752716849</v>
       </c>
       <c r="O16" t="n">
-        <v>181.0500921949917</v>
+        <v>297.3129142515843</v>
       </c>
       <c r="P16" t="n">
-        <v>436.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>474.839266425598</v>
@@ -23894,16 +23894,16 @@
         <v>292.1850752716849</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>361.445564079015</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q19" t="n">
-        <v>430.4918320509146</v>
+        <v>108.2004986247733</v>
       </c>
       <c r="R19" t="n">
-        <v>447.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>83.37347970285543</v>
@@ -24137,10 +24137,10 @@
         <v>408.4478973282775</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>108.2004986247733</v>
       </c>
       <c r="R22" t="n">
-        <v>108.2004986247733</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>83.37347970285543</v>
@@ -24408,10 +24408,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>256.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>224.4745782429939</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -24420,10 +24420,10 @@
         <v>179.3632896068686</v>
       </c>
       <c r="F26" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>154.0669925793889</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -24465,7 +24465,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>424.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -24477,7 +24477,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>105.7082543504233</v>
       </c>
     </row>
     <row r="27">
@@ -24651,19 +24651,19 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>165.3391557398498</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>159.3632896068686</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>159.8896287080119</v>
       </c>
       <c r="G29" t="n">
-        <v>111.017457911993</v>
+        <v>158.7573722870162</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1.953361101133282</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24696,10 +24696,10 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>254.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>346.6755817285639</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -24803,22 +24803,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>47.11380033707866</v>
+        <v>42.11380033707866</v>
       </c>
       <c r="C31" t="n">
-        <v>32.72524664804467</v>
+        <v>27.72524664804467</v>
       </c>
       <c r="D31" t="n">
-        <v>45.53621805555548</v>
+        <v>40.53621805555548</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>34.38285596774193</v>
+        <v>29.38285596774193</v>
       </c>
       <c r="G31" t="n">
-        <v>5.043872841530032</v>
+        <v>0.04387284153003179</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -24830,31 +24830,31 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>48.52077380114304</v>
+        <v>43.52077380114304</v>
       </c>
       <c r="L31" t="n">
-        <v>183.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>280.6316114025499</v>
+        <v>275.6316114025499</v>
       </c>
       <c r="N31" t="n">
-        <v>331.1850752716849</v>
+        <v>326.1850752716849</v>
       </c>
       <c r="O31" t="n">
-        <v>400.445564079015</v>
+        <v>395.445564079015</v>
       </c>
       <c r="P31" t="n">
-        <v>447.4478973282775</v>
+        <v>442.4478973282775</v>
       </c>
       <c r="Q31" t="n">
-        <v>83.03050744881432</v>
+        <v>480.839266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>486.6021279811511</v>
+        <v>218.0374971621466</v>
       </c>
       <c r="S31" t="n">
-        <v>122.3734797028554</v>
+        <v>117.3734797028554</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -24869,10 +24869,10 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>7.443645430107551</v>
+        <v>2.443645430107551</v>
       </c>
       <c r="Y31" t="n">
-        <v>47.46535284946236</v>
+        <v>42.46535284946236</v>
       </c>
     </row>
     <row r="32">
@@ -24897,7 +24897,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>9.424208614585737</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -24936,7 +24936,7 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>1.662608614585338</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -25070,28 +25070,28 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>133.5476281577792</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>230.6316114025499</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>281.1850752716849</v>
       </c>
       <c r="O34" t="n">
         <v>350.445564079015</v>
       </c>
       <c r="P34" t="n">
-        <v>397.4478973282775</v>
+        <v>345.078966540631</v>
       </c>
       <c r="Q34" t="n">
-        <v>435.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>229.5295973216249</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>72.37347970285543</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25119,7 +25119,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>9.424208614562787</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -25170,7 +25170,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.662608614585082</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -25313,7 +25313,7 @@
         <v>230.6316114025499</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>281.1850752716849</v>
       </c>
       <c r="O37" t="n">
         <v>350.445564079015</v>
@@ -25322,13 +25322,13 @@
         <v>397.4478973282775</v>
       </c>
       <c r="Q37" t="n">
-        <v>228.8161444840384</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>72.37347970285543</v>
+        <v>20.00454891520893</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25356,7 +25356,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>9.424208614585723</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -25416,7 +25416,7 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.662608614585395</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
@@ -25553,16 +25553,16 @@
         <v>281.1850752716849</v>
       </c>
       <c r="O40" t="n">
-        <v>350.445564079015</v>
+        <v>258.9224026384949</v>
       </c>
       <c r="P40" t="n">
-        <v>345.078966540631</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>436.6021279811511</v>
       </c>
       <c r="S40" t="n">
         <v>72.37347970285543</v>
@@ -25593,22 +25593,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>271.9993129555745</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>80.88594076881817</v>
+        <v>200.3391557398498</v>
       </c>
       <c r="E41" t="n">
-        <v>195.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>195.8896287080119</v>
+        <v>194.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>63.8534134908337</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -25641,16 +25641,16 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>41.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>285.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>377.6755817285639</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>439.2212965486107</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -25720,10 +25720,10 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>221.7887581423993</v>
       </c>
       <c r="S42" t="n">
-        <v>26.53422560992965</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
@@ -25735,7 +25735,7 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>223.3731429098285</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -25751,22 +25751,22 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>78.11380033707866</v>
+        <v>77.11380033707866</v>
       </c>
       <c r="C43" t="n">
-        <v>63.72524664804467</v>
+        <v>62.72524664804467</v>
       </c>
       <c r="D43" t="n">
-        <v>76.53621805555548</v>
+        <v>75.53621805555548</v>
       </c>
       <c r="E43" t="n">
-        <v>71.98090483695654</v>
+        <v>70.98090483695654</v>
       </c>
       <c r="F43" t="n">
-        <v>65.38285596774193</v>
+        <v>64.38285596774193</v>
       </c>
       <c r="G43" t="n">
-        <v>36.04387284153003</v>
+        <v>35.04387284153003</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -25778,31 +25778,31 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>79.52077380114304</v>
+        <v>78.52077380114304</v>
       </c>
       <c r="L43" t="n">
-        <v>214.5476281577792</v>
+        <v>213.5476281577792</v>
       </c>
       <c r="M43" t="n">
-        <v>311.6316114025499</v>
+        <v>310.6316114025499</v>
       </c>
       <c r="N43" t="n">
-        <v>362.1850752716849</v>
+        <v>361.1850752716849</v>
       </c>
       <c r="O43" t="n">
-        <v>431.445564079015</v>
+        <v>430.445564079015</v>
       </c>
       <c r="P43" t="n">
-        <v>478.4478973282775</v>
+        <v>477.4478973282775</v>
       </c>
       <c r="Q43" t="n">
-        <v>516.839266425598</v>
+        <v>515.839266425598</v>
       </c>
       <c r="R43" t="n">
-        <v>517.6021279811511</v>
+        <v>516.6021279811511</v>
       </c>
       <c r="S43" t="n">
-        <v>153.3734797028554</v>
+        <v>152.3734797028554</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -25817,10 +25817,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>38.44364543010755</v>
+        <v>37.44364543010755</v>
       </c>
       <c r="Y43" t="n">
-        <v>78.46535284946236</v>
+        <v>77.46535284946236</v>
       </c>
     </row>
     <row r="44">
@@ -25830,25 +25830,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>313.9993129555745</v>
+        <v>192.0815132638451</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>285.4745782429939</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>240.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>240.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>235.7573722870162</v>
+        <v>239.7573722870162</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>244.0096587035274</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25878,13 +25878,13 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>86.87859882829446</v>
       </c>
       <c r="S44" t="n">
-        <v>326.8481678023229</v>
+        <v>330.8481678023229</v>
       </c>
       <c r="T44" t="n">
-        <v>21.28104495635137</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -25893,10 +25893,10 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>470.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>424.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -25909,25 +25909,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>216.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>183.9376868977026</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>171.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>161.7395358750273</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>168.1680871864211</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -25954,25 +25954,25 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>5.079265090479588</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>379.2737972923793</v>
+        <v>383.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>20.43257524886167</v>
+        <v>302.5639999646113</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>232.2103597601867</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>264.3731429098285</v>
+        <v>268.3731429098285</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -25988,76 +25988,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>119.1138003370787</v>
+        <v>123.1138003370787</v>
       </c>
       <c r="C46" t="n">
-        <v>104.7252466480447</v>
+        <v>108.7252466480447</v>
       </c>
       <c r="D46" t="n">
-        <v>117.5362180555555</v>
+        <v>121.5362180555555</v>
       </c>
       <c r="E46" t="n">
-        <v>112.9809048369565</v>
+        <v>116.9809048369565</v>
       </c>
       <c r="F46" t="n">
-        <v>106.3828559677419</v>
+        <v>110.3828559677419</v>
       </c>
       <c r="G46" t="n">
-        <v>77.04387284153003</v>
+        <v>81.04387284153003</v>
       </c>
       <c r="H46" t="n">
-        <v>60.77112610161862</v>
+        <v>64.77112610161862</v>
       </c>
       <c r="I46" t="n">
-        <v>8.633455620118273</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>120.520773801143</v>
+        <v>124.520773801143</v>
       </c>
       <c r="L46" t="n">
-        <v>255.5476281577792</v>
+        <v>259.5476281577792</v>
       </c>
       <c r="M46" t="n">
-        <v>352.6316114025499</v>
+        <v>356.6316114025499</v>
       </c>
       <c r="N46" t="n">
-        <v>403.1850752716849</v>
+        <v>407.1850752716849</v>
       </c>
       <c r="O46" t="n">
-        <v>472.445564079015</v>
+        <v>476.445564079015</v>
       </c>
       <c r="P46" t="n">
-        <v>519.4478973282775</v>
+        <v>523.4478973282775</v>
       </c>
       <c r="Q46" t="n">
-        <v>557.839266425598</v>
+        <v>561.839266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>558.6021279811511</v>
+        <v>562.6021279811511</v>
       </c>
       <c r="S46" t="n">
-        <v>194.3734797028554</v>
+        <v>198.3734797028554</v>
       </c>
       <c r="T46" t="n">
-        <v>42.02456650625771</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>31.17031021621619</v>
+        <v>19.86586636391455</v>
       </c>
       <c r="W46" t="n">
-        <v>58.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>79.44364543010755</v>
+        <v>83.44364543010755</v>
       </c>
       <c r="Y46" t="n">
-        <v>119.4653528494624</v>
+        <v>123.4653528494624</v>
       </c>
     </row>
   </sheetData>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>989929.9725264019</v>
+        <v>989382.2691658493</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1840009.474750903</v>
+        <v>1839536.271489664</v>
       </c>
     </row>
     <row r="4">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2690088.976975405</v>
+        <v>2689615.773714167</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3448946.582096091</v>
+        <v>3448473.378834853</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4240221.583561567</v>
+        <v>4239748.380300329</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5063175.015154023</v>
+        <v>5062701.811892785</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5886128.446746477</v>
+        <v>5885655.243485238</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6709081.87833893</v>
+        <v>6708608.675077693</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7457257.155659369</v>
+        <v>7456193.570519022</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8226875.189159656</v>
+        <v>8231357.039951308</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9055040.228108775</v>
+        <v>9059278.399243537</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9882135.548704913</v>
+        <v>9885956.689071679</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10709230.86930106</v>
+        <v>10712634.97889982</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>11429915.59300755</v>
+        <v>11434615.42535621</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12074324.02050551</v>
+        <v>12071057.54637817</v>
       </c>
     </row>
   </sheetData>
@@ -26269,16 +26269,16 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>1353076.698348901</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1353830.318357539</v>
+      </c>
+      <c r="D2" t="n">
         <v>1353830.31835754</v>
       </c>
-      <c r="C2" t="n">
-        <v>1353830.31835754</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1353830.318357539</v>
-      </c>
       <c r="E2" t="n">
-        <v>1210813.279674651</v>
+        <v>1210813.27967465</v>
       </c>
       <c r="F2" t="n">
         <v>1260178.706037608</v>
@@ -26287,31 +26287,31 @@
         <v>1310629.539202803</v>
       </c>
       <c r="H2" t="n">
-        <v>1310629.539202804</v>
+        <v>1310629.539202803</v>
       </c>
       <c r="I2" t="n">
         <v>1310629.539202803</v>
       </c>
       <c r="J2" t="n">
-        <v>1197197.99737865</v>
+        <v>1196533.837266651</v>
       </c>
       <c r="K2" t="n">
-        <v>1225687.979278241</v>
+        <v>1234519.59946624</v>
       </c>
       <c r="L2" t="n">
-        <v>1317225.880949402</v>
+        <v>1316561.720837403</v>
       </c>
       <c r="M2" t="n">
-        <v>1317225.880949402</v>
+        <v>1316561.720837404</v>
       </c>
       <c r="N2" t="n">
-        <v>1317225.880949402</v>
+        <v>1316561.720837403</v>
       </c>
       <c r="O2" t="n">
-        <v>1149460.778094715</v>
+        <v>1151800.414243715</v>
       </c>
       <c r="P2" t="n">
-        <v>1026280.088237493</v>
+        <v>1013593.007553493</v>
       </c>
     </row>
     <row r="3">
@@ -26321,10 +26321,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>286880</v>
+        <v>286528</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -26345,13 +26345,13 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>409248</v>
+        <v>408192</v>
       </c>
       <c r="K3" t="n">
-        <v>32800</v>
+        <v>37152</v>
       </c>
       <c r="L3" t="n">
-        <v>62400</v>
+        <v>58400</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -26360,7 +26360,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>72000</v>
+        <v>72800</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>575920.3474495769</v>
+        <v>580502.3723909451</v>
       </c>
       <c r="C4" t="n">
-        <v>574167.5049491362</v>
+        <v>579056.6613370483</v>
       </c>
       <c r="D4" t="n">
-        <v>572412.2846084388</v>
+        <v>577301.4409963506</v>
       </c>
       <c r="E4" t="n">
-        <v>493973.8046613694</v>
+        <v>498813.3005071199</v>
       </c>
       <c r="F4" t="n">
-        <v>518248.4204553652</v>
+        <v>523087.9163011156</v>
       </c>
       <c r="G4" t="n">
-        <v>542883.6451658959</v>
+        <v>547723.1410116464</v>
       </c>
       <c r="H4" t="n">
-        <v>541211.3456360602</v>
+        <v>546050.8414818107</v>
       </c>
       <c r="I4" t="n">
-        <v>539536.711548938</v>
+        <v>544376.2073946885</v>
       </c>
       <c r="J4" t="n">
-        <v>483155.4430213695</v>
+        <v>487692.6735574823</v>
       </c>
       <c r="K4" t="n">
-        <v>496231.9981181989</v>
+        <v>505616.3892984667</v>
       </c>
       <c r="L4" t="n">
-        <v>542612.5255668919</v>
+        <v>547411.7513770948</v>
       </c>
       <c r="M4" t="n">
-        <v>540884.7470208164</v>
+        <v>545683.9728310208</v>
       </c>
       <c r="N4" t="n">
-        <v>539154.4842164956</v>
+        <v>543953.7100266985</v>
       </c>
       <c r="O4" t="n">
-        <v>451612.6755590176</v>
+        <v>457672.1890892775</v>
       </c>
       <c r="P4" t="n">
-        <v>388098.7572540884</v>
+        <v>386573.6380117485</v>
       </c>
     </row>
     <row r="5">
@@ -26425,7 +26425,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>83179.60000000001</v>
+        <v>83118.79999999999</v>
       </c>
       <c r="C5" t="n">
         <v>83179.60000000001</v>
@@ -26449,25 +26449,25 @@
         <v>73007.251</v>
       </c>
       <c r="J5" t="n">
-        <v>65974.72500000001</v>
+        <v>65853.125</v>
       </c>
       <c r="K5" t="n">
-        <v>67235.75999999999</v>
+        <v>67534.505</v>
       </c>
       <c r="L5" t="n">
-        <v>71439.20999999999</v>
+        <v>71317.61</v>
       </c>
       <c r="M5" t="n">
-        <v>71439.20999999999</v>
+        <v>71317.61</v>
       </c>
       <c r="N5" t="n">
-        <v>71439.20999999999</v>
+        <v>71317.61</v>
       </c>
       <c r="O5" t="n">
-        <v>64629.621</v>
+        <v>64592.09</v>
       </c>
       <c r="P5" t="n">
-        <v>61182.792</v>
+        <v>60724.916</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>407850.3709079629</v>
+        <v>402927.5259579555</v>
       </c>
       <c r="C6" t="n">
-        <v>696483.2134084037</v>
+        <v>691242.0570204909</v>
       </c>
       <c r="D6" t="n">
-        <v>698238.4337491001</v>
+        <v>693349.277361189</v>
       </c>
       <c r="E6" t="n">
-        <v>468371.9500132812</v>
+        <v>463532.4541675305</v>
       </c>
       <c r="F6" t="n">
-        <v>650476.9665822432</v>
+        <v>645637.4707364928</v>
       </c>
       <c r="G6" t="n">
-        <v>672338.6430369071</v>
+        <v>667499.1471911566</v>
       </c>
       <c r="H6" t="n">
-        <v>696410.9425667435</v>
+        <v>691571.4467209923</v>
       </c>
       <c r="I6" t="n">
-        <v>698085.576653865</v>
+        <v>693246.0808081143</v>
       </c>
       <c r="J6" t="n">
-        <v>238819.8293572804</v>
+        <v>234796.0387091685</v>
       </c>
       <c r="K6" t="n">
-        <v>629420.2211600416</v>
+        <v>624216.7051677733</v>
       </c>
       <c r="L6" t="n">
-        <v>640774.1453825106</v>
+        <v>639432.3594603081</v>
       </c>
       <c r="M6" t="n">
-        <v>704901.9239285858</v>
+        <v>699560.1380063834</v>
       </c>
       <c r="N6" t="n">
-        <v>706632.1867329066</v>
+        <v>701290.4008107046</v>
       </c>
       <c r="O6" t="n">
-        <v>561218.4815356976</v>
+        <v>556736.1351544376</v>
       </c>
       <c r="P6" t="n">
-        <v>576998.538983405</v>
+        <v>566294.4535417447</v>
       </c>
     </row>
   </sheetData>
@@ -26782,7 +26782,7 @@
         <v>225</v>
       </c>
       <c r="K2" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="L2" t="n">
         <v>290</v>
@@ -26794,10 +26794,10 @@
         <v>290</v>
       </c>
       <c r="O2" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P2" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3">
@@ -26859,7 +26859,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C4" t="n">
         <v>815</v>
@@ -26883,25 +26883,25 @@
         <v>815</v>
       </c>
       <c r="J4" t="n">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="K4" t="n">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="L4" t="n">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="M4" t="n">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="N4" t="n">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="O4" t="n">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="P4" t="n">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
   </sheetData>
@@ -26978,7 +26978,7 @@
         <v>-0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>225</v>
@@ -26990,7 +26990,7 @@
         <v>28</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
         <v>-0</v>
@@ -26999,19 +26999,19 @@
         <v>171</v>
       </c>
       <c r="K2" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L2" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P2" t="n">
         <v>-0</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27076,10 +27076,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>-0</v>
@@ -27100,10 +27100,10 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>-0</v>
@@ -27231,7 +27231,7 @@
         <v>171</v>
       </c>
       <c r="P2" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
@@ -27317,10 +27317,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -27445,11 +27445,11 @@
         <v>400</v>
       </c>
       <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
         <v>400</v>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
@@ -27487,7 +27487,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>303.5095671255643</v>
+        <v>307.3903671255649</v>
       </c>
       <c r="U2" t="n">
         <v>400</v>
@@ -27515,19 +27515,19 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>168.7500662750008</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>332.1680871864211</v>
@@ -27566,7 +27566,7 @@
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>400</v>
+        <v>210.6860087135173</v>
       </c>
       <c r="U3" t="n">
         <v>400</v>
@@ -27597,28 +27597,28 @@
         <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
         <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>393.0146752152657</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H4" t="n">
         <v>228.7711261016186</v>
       </c>
       <c r="I4" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
         <v>35.26894883590776</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27642,10 +27642,10 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T4" t="n">
-        <v>400</v>
+        <v>392.0660536684909</v>
       </c>
       <c r="U4" t="n">
         <v>400</v>
@@ -27657,10 +27657,10 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5">
@@ -27685,10 +27685,10 @@
         <v>400</v>
       </c>
       <c r="G5" t="n">
-        <v>303.5095671255647</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>303.5095671255648</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -27724,10 +27724,10 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="U5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>400</v>
@@ -27749,28 +27749,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>274.7686191606065</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>27.81239460486586</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>332.1680871864211</v>
       </c>
       <c r="I6" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27806,7 +27806,7 @@
         <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="V6" t="n">
         <v>400</v>
@@ -27834,10 +27834,10 @@
         <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
-        <v>336.2326479955244</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
         <v>274.3828559677419</v>
@@ -27846,16 +27846,16 @@
         <v>245.04387284153</v>
       </c>
       <c r="H7" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J7" t="n">
         <v>35.26894883590776</v>
       </c>
       <c r="K7" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27879,13 +27879,13 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T7" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U7" t="n">
-        <v>400</v>
+        <v>291.242834416779</v>
       </c>
       <c r="V7" t="n">
         <v>400</v>
@@ -27910,10 +27910,10 @@
         <v>400</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E8" t="n">
         <v>400</v>
@@ -27922,10 +27922,10 @@
         <v>400</v>
       </c>
       <c r="G8" t="n">
+        <v>52.63096829727033</v>
+      </c>
+      <c r="H8" t="n">
         <v>400</v>
-      </c>
-      <c r="H8" t="n">
-        <v>52.63096829727016</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -27958,7 +27958,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -27970,13 +27970,13 @@
         <v>400</v>
       </c>
       <c r="W8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -27992,13 +27992,13 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>172.5204020740694</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>284.3378656046244</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
         <v>325.7395358750273</v>
@@ -28049,13 +28049,13 @@
         <v>400</v>
       </c>
       <c r="W9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -28074,13 +28074,13 @@
         <v>400</v>
       </c>
       <c r="E10" t="n">
-        <v>400</v>
+        <v>373.8591682926689</v>
       </c>
       <c r="F10" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
-        <v>283.2613305956833</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H10" t="n">
         <v>228.7711261016186</v>
@@ -28119,7 +28119,7 @@
         <v>362.3734797028554</v>
       </c>
       <c r="T10" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U10" t="n">
         <v>400</v>
@@ -28250,13 +28250,13 @@
         <v>225</v>
       </c>
       <c r="K12" t="n">
-        <v>19.1168712588393</v>
+        <v>225</v>
       </c>
       <c r="L12" t="n">
         <v>225</v>
       </c>
       <c r="M12" t="n">
-        <v>225</v>
+        <v>19.11687125883925</v>
       </c>
       <c r="N12" t="n">
         <v>225</v>
@@ -28484,25 +28484,25 @@
         <v>251</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="M15" t="n">
         <v>166.1982915220774</v>
       </c>
       <c r="N15" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>251</v>
@@ -28630,7 +28630,7 @@
         <v>279</v>
       </c>
       <c r="F17" t="n">
-        <v>279</v>
+        <v>275.549808614586</v>
       </c>
       <c r="G17" t="n">
         <v>279</v>
@@ -28639,7 +28639,7 @@
         <v>279</v>
       </c>
       <c r="I17" t="n">
-        <v>146.6309682972706</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28718,13 +28718,13 @@
         <v>279</v>
       </c>
       <c r="I18" t="n">
-        <v>279</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>261.5913251766234</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -28736,13 +28736,13 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>217.5442043757546</v>
       </c>
       <c r="P18" t="n">
         <v>279</v>
       </c>
       <c r="Q18" t="n">
-        <v>173.0792650904796</v>
+        <v>279</v>
       </c>
       <c r="R18" t="n">
         <v>279</v>
@@ -28873,10 +28873,10 @@
         <v>279</v>
       </c>
       <c r="H20" t="n">
-        <v>275.549808614586</v>
+        <v>279</v>
       </c>
       <c r="I20" t="n">
-        <v>150.0811596826846</v>
+        <v>146.6309682972706</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28961,25 +28961,25 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>155.6705902671029</v>
+      </c>
+      <c r="O21" t="n">
         <v>279</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>261.5913251766233</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>173.0792650904796</v>
+        <v>279</v>
       </c>
       <c r="R21" t="n">
         <v>279</v>
@@ -29110,10 +29110,10 @@
         <v>279</v>
       </c>
       <c r="H23" t="n">
-        <v>275.549808614586</v>
+        <v>279</v>
       </c>
       <c r="I23" t="n">
-        <v>150.0811596826846</v>
+        <v>146.6309682972706</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29195,10 +29195,10 @@
         <v>217.1263858913485</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -29210,13 +29210,13 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>217.5442043757546</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>279</v>
+        <v>217.5442043757548</v>
       </c>
       <c r="R24" t="n">
         <v>279</v>
@@ -29350,7 +29350,7 @@
         <v>225</v>
       </c>
       <c r="I26" t="n">
-        <v>150.0811596826846</v>
+        <v>150.081159682688</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29432,7 +29432,7 @@
         <v>225</v>
       </c>
       <c r="J27" t="n">
-        <v>19.11687125883908</v>
+        <v>19.11687125883925</v>
       </c>
       <c r="K27" t="n">
         <v>225</v>
@@ -29566,25 +29566,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C29" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D29" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E29" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="F29" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="G29" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="H29" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="I29" t="n">
         <v>150.0811596826846</v>
@@ -29614,28 +29614,28 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="S29" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="T29" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="U29" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="V29" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="W29" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="X29" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="Y29" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="30">
@@ -29645,76 +29645,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C30" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D30" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E30" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="F30" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="G30" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="H30" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="I30" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="J30" t="n">
-        <v>149.5484598722458</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="M30" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>240</v>
+        <v>43.02565607671426</v>
       </c>
       <c r="O30" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="P30" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="Q30" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="R30" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="S30" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="T30" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="U30" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="V30" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="W30" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="X30" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="Y30" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="31">
@@ -29724,76 +29724,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C31" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D31" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E31" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="F31" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="G31" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="H31" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="I31" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="J31" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="K31" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="L31" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="M31" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="N31" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="O31" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="P31" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="Q31" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="R31" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="S31" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="T31" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="U31" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="V31" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="W31" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="X31" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="Y31" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="32">
@@ -29903,28 +29903,28 @@
         <v>290</v>
       </c>
       <c r="I33" t="n">
-        <v>244.3204219169347</v>
+        <v>244.3204219169348</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
         <v>290</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>290</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>250.8785988282945</v>
+        <v>250.8785988283179</v>
       </c>
       <c r="S35" t="n">
         <v>290</v>
@@ -30140,7 +30140,7 @@
         <v>290</v>
       </c>
       <c r="I36" t="n">
-        <v>244.3204219169346</v>
+        <v>244.3204219169348</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30377,31 +30377,31 @@
         <v>290</v>
       </c>
       <c r="I39" t="n">
+        <v>244.3204219169349</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
         <v>290</v>
       </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
         <v>290</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>244.320421916935</v>
       </c>
       <c r="R39" t="n">
         <v>290</v>
@@ -30514,25 +30514,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I41" t="n">
         <v>150.0811596826846</v>
@@ -30562,28 +30562,28 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="S41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="T41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="U41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="V41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="W41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="X41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Y41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="42">
@@ -30593,76 +30593,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L42" t="n">
-        <v>137.173341577663</v>
+        <v>210</v>
       </c>
       <c r="M42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P42" t="n">
-        <v>209</v>
+        <v>142.5380088334109</v>
       </c>
       <c r="Q42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="R42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="S42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="T42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="U42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="V42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="W42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="X42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Y42" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="43">
@@ -30672,76 +30672,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I43" t="n">
-        <v>209</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J43" t="n">
         <v>35.26894883590776</v>
       </c>
       <c r="K43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="R43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="S43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="T43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="U43" t="n">
-        <v>157.5353245464342</v>
+        <v>186.8409567744947</v>
       </c>
       <c r="V43" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="X43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Y43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="44">
@@ -30751,25 +30751,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C44" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D44" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E44" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F44" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G44" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="H44" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I44" t="n">
         <v>150.0811596826846</v>
@@ -30799,28 +30799,28 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="S44" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="T44" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="U44" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="V44" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="W44" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="X44" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="Y44" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="45">
@@ -30830,76 +30830,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C45" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D45" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E45" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F45" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G45" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="H45" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I45" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J45" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="K45" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="L45" t="n">
-        <v>32.83215864645134</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>168</v>
+        <v>108.09436572733</v>
       </c>
       <c r="N45" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="O45" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="P45" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="Q45" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="R45" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="S45" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="T45" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="U45" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="V45" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="W45" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="X45" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="Y45" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="46">
@@ -30909,76 +30909,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C46" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D46" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E46" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F46" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G46" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="H46" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I46" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J46" t="n">
-        <v>35.26894883590776</v>
+        <v>164</v>
       </c>
       <c r="K46" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="L46" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M46" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="N46" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="O46" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="P46" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="Q46" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="R46" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="S46" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="T46" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="U46" t="n">
-        <v>150.9583912744579</v>
+        <v>161.3307742674796</v>
       </c>
       <c r="V46" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="W46" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="X46" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="Y46" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -34743,28 +34743,28 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="K2" t="n">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="L2" t="n">
-        <v>783.0093003025929</v>
+        <v>814</v>
       </c>
       <c r="M2" t="n">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N2" t="n">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="O2" t="n">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="P2" t="n">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="Q2" t="n">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34883,28 +34883,28 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
         <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>147.9708023737357</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,10 +34928,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>189.9754334937423</v>
+        <v>182.0414871622332</v>
       </c>
       <c r="U4" t="n">
         <v>249.0416087255421</v>
@@ -34943,10 +34943,10 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -34983,7 +34983,7 @@
         <v>815</v>
       </c>
       <c r="K5" t="n">
-        <v>783.0093003025894</v>
+        <v>783.0093003026486</v>
       </c>
       <c r="L5" t="n">
         <v>815</v>
@@ -35120,10 +35120,10 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>55.25174315856783</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -35132,16 +35132,16 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35165,13 +35165,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0416087255421</v>
+        <v>140.284443142321</v>
       </c>
       <c r="V7" t="n">
         <v>200.8296897837838</v>
@@ -35220,10 +35220,10 @@
         <v>815</v>
       </c>
       <c r="K8" t="n">
-        <v>783.0093003026934</v>
+        <v>815</v>
       </c>
       <c r="L8" t="n">
-        <v>815</v>
+        <v>783.0093003025238</v>
       </c>
       <c r="M8" t="n">
         <v>815</v>
@@ -35360,13 +35360,13 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>92.87826345571237</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>38.21745775415324</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -35405,7 +35405,7 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U10" t="n">
         <v>249.0416087255421</v>
@@ -35460,7 +35460,7 @@
         <v>716.8751175230996</v>
       </c>
       <c r="L11" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
@@ -35469,13 +35469,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O11" t="n">
-        <v>164.5104768795733</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>536.4810879374849</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35536,13 +35536,13 @@
         <v>350.2086062376757</v>
       </c>
       <c r="K12" t="n">
-        <v>210.2207258996306</v>
+        <v>416.1038546407913</v>
       </c>
       <c r="L12" t="n">
         <v>499.091375348687</v>
       </c>
       <c r="M12" t="n">
-        <v>311.9500421645043</v>
+        <v>106.0669134233435</v>
       </c>
       <c r="N12" t="n">
         <v>359.6265501086548</v>
@@ -35694,16 +35694,16 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>619.4144644189528</v>
+        <v>41.9044702644529</v>
       </c>
       <c r="O14" t="n">
         <v>815</v>
@@ -35712,7 +35712,7 @@
         <v>815</v>
       </c>
       <c r="Q14" t="n">
-        <v>66.38559440267282</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35770,25 +35770,25 @@
         <v>33.87361410865147</v>
       </c>
       <c r="J15" t="n">
-        <v>125.2086062376757</v>
+        <v>376.2086062376757</v>
       </c>
       <c r="K15" t="n">
-        <v>191.1038546407913</v>
+        <v>442.1038546407913</v>
       </c>
       <c r="L15" t="n">
-        <v>274.091375348687</v>
+        <v>525.0913753486871</v>
       </c>
       <c r="M15" t="n">
         <v>253.1483336865817</v>
       </c>
       <c r="N15" t="n">
-        <v>385.6265501086548</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O15" t="n">
-        <v>492.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P15" t="n">
-        <v>364.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q15" t="n">
         <v>77.92073490952041</v>
@@ -35931,25 +35931,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>139.3651233685997</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>815</v>
       </c>
       <c r="Q17" t="n">
-        <v>443.0293889420883</v>
+        <v>164.5104768795733</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36004,13 +36004,13 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>61.87361410865147</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>125.2086062376757</v>
       </c>
       <c r="K18" t="n">
-        <v>452.6951798174147</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L18" t="n">
         <v>274.091375348687</v>
@@ -36022,13 +36022,13 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O18" t="n">
-        <v>241.4570219027464</v>
+        <v>459.001226278501</v>
       </c>
       <c r="P18" t="n">
         <v>392.6660045146532</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>105.9207349095204</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36165,25 +36165,25 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>814.9999999999999</v>
+        <v>242.7706698795373</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>116.7428182785516</v>
+        <v>815</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="Q20" t="n">
         <v>443.0293889420883</v>
@@ -36247,25 +36247,25 @@
         <v>125.2086062376757</v>
       </c>
       <c r="K21" t="n">
-        <v>470.1038546407913</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L21" t="n">
         <v>274.091375348687</v>
       </c>
       <c r="M21" t="n">
-        <v>348.5413673411276</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N21" t="n">
-        <v>134.6265501086548</v>
+        <v>290.2971403757577</v>
       </c>
       <c r="O21" t="n">
-        <v>241.4570219027464</v>
+        <v>520.4570219027464</v>
       </c>
       <c r="P21" t="n">
         <v>113.6660045146532</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>105.9207349095204</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36402,7 +36402,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>395.2617303410664</v>
+        <v>18.61793580165097</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -36417,7 +36417,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O23" t="n">
-        <v>438.3562054605844</v>
+        <v>815</v>
       </c>
       <c r="P23" t="n">
         <v>815</v>
@@ -36481,10 +36481,10 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>125.2086062376757</v>
+        <v>404.2086062376757</v>
       </c>
       <c r="K24" t="n">
-        <v>191.1038546407913</v>
+        <v>470.1038546407913</v>
       </c>
       <c r="L24" t="n">
         <v>274.091375348687</v>
@@ -36496,13 +36496,13 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O24" t="n">
-        <v>520.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P24" t="n">
-        <v>331.2102088904077</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q24" t="n">
-        <v>105.9207349095204</v>
+        <v>44.46493928527515</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36636,28 +36636,28 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>3.351752096969361e-12</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>614.8138483540246</v>
+        <v>772</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>311.0935791979583</v>
       </c>
       <c r="P26" t="n">
-        <v>774.0000000000454</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>443.0293889420883</v>
@@ -36718,7 +36718,7 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J27" t="n">
-        <v>144.3254774965148</v>
+        <v>144.3254774965149</v>
       </c>
       <c r="K27" t="n">
         <v>416.1038546407913</v>
@@ -36879,25 +36879,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>678.4361534441181</v>
+        <v>601.5374325589873</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>774</v>
+        <v>772.0000000000064</v>
       </c>
       <c r="P29" t="n">
-        <v>774</v>
+        <v>772.0000000000058</v>
       </c>
       <c r="Q29" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -36952,31 +36952,31 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>22.87361410865147</v>
+        <v>27.87361410865147</v>
       </c>
       <c r="J30" t="n">
-        <v>274.7570661099214</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K30" t="n">
-        <v>191.1038546407913</v>
+        <v>436.1038546407913</v>
       </c>
       <c r="L30" t="n">
-        <v>274.091375348687</v>
+        <v>519.0913753486871</v>
       </c>
       <c r="M30" t="n">
-        <v>326.9500421645043</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N30" t="n">
-        <v>374.6265501086548</v>
+        <v>177.6522061853691</v>
       </c>
       <c r="O30" t="n">
-        <v>481.4570219027464</v>
+        <v>486.4570219027464</v>
       </c>
       <c r="P30" t="n">
-        <v>353.6660045146532</v>
+        <v>358.6660045146532</v>
       </c>
       <c r="Q30" t="n">
-        <v>66.92073490952041</v>
+        <v>71.92073490952041</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37028,13 +37028,13 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>11.22887389838138</v>
+        <v>16.22887389838138</v>
       </c>
       <c r="I31" t="n">
-        <v>63.36654437988173</v>
+        <v>68.36654437988173</v>
       </c>
       <c r="J31" t="n">
-        <v>204.7310511640922</v>
+        <v>209.7310511640922</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -37064,16 +37064,16 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>29.97543349374229</v>
+        <v>34.97543349374229</v>
       </c>
       <c r="U31" t="n">
-        <v>89.04160872554206</v>
+        <v>94.04160872554206</v>
       </c>
       <c r="V31" t="n">
-        <v>40.82968978378381</v>
+        <v>45.82968978378381</v>
       </c>
       <c r="W31" t="n">
-        <v>13.62719016129032</v>
+        <v>18.62719016129032</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -37113,28 +37113,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="K32" t="n">
-        <v>716.8751175230994</v>
+        <v>506.4308407844085</v>
       </c>
       <c r="L32" t="n">
-        <v>159.5255725075646</v>
+        <v>772</v>
       </c>
       <c r="M32" t="n">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="N32" t="n">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="O32" t="n">
-        <v>774</v>
+        <v>772.0000000000073</v>
       </c>
       <c r="P32" t="n">
-        <v>774</v>
+        <v>772.0000000000067</v>
       </c>
       <c r="Q32" t="n">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37189,13 +37189,13 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>27.19403602558619</v>
+        <v>27.19403602558626</v>
       </c>
       <c r="J33" t="n">
         <v>125.2086062376757</v>
       </c>
       <c r="K33" t="n">
-        <v>481.1038546407913</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L33" t="n">
         <v>274.091375348687</v>
@@ -37210,7 +37210,7 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P33" t="n">
-        <v>113.6660045146532</v>
+        <v>403.6660045146532</v>
       </c>
       <c r="Q33" t="n">
         <v>116.9207349095204</v>
@@ -37350,31 +37350,31 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="K35" t="n">
-        <v>102.4006900306321</v>
+        <v>772</v>
       </c>
       <c r="L35" t="n">
-        <v>774</v>
+        <v>506.4308407852416</v>
       </c>
       <c r="M35" t="n">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="N35" t="n">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="O35" t="n">
-        <v>774</v>
+        <v>772.0000000000073</v>
       </c>
       <c r="P35" t="n">
-        <v>774</v>
+        <v>772.0000000000067</v>
       </c>
       <c r="Q35" t="n">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.342637868202997e-11</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -37426,7 +37426,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>27.19403602558611</v>
+        <v>27.19403602558626</v>
       </c>
       <c r="J36" t="n">
         <v>125.2086062376757</v>
@@ -37587,28 +37587,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="K38" t="n">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="L38" t="n">
-        <v>102.4006900306321</v>
+        <v>506.4308407844114</v>
       </c>
       <c r="M38" t="n">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="N38" t="n">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="O38" t="n">
-        <v>774</v>
+        <v>772.0000000000073</v>
       </c>
       <c r="P38" t="n">
-        <v>774</v>
+        <v>772.0000000000067</v>
       </c>
       <c r="Q38" t="n">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37663,13 +37663,13 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>72.87361410865147</v>
+        <v>27.19403602558637</v>
       </c>
       <c r="J39" t="n">
         <v>125.2086062376757</v>
       </c>
       <c r="K39" t="n">
-        <v>481.1038546407913</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L39" t="n">
         <v>274.091375348687</v>
@@ -37678,7 +37678,7 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N39" t="n">
-        <v>134.6265501086548</v>
+        <v>424.6265501086548</v>
       </c>
       <c r="O39" t="n">
         <v>241.4570219027464</v>
@@ -37687,7 +37687,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q39" t="n">
-        <v>71.24115682645539</v>
+        <v>116.9207349095204</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37827,25 +37827,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>774</v>
+        <v>674.5169615249122</v>
       </c>
       <c r="M41" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>772.0000000000073</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>772.0000000000067</v>
       </c>
       <c r="Q41" t="n">
-        <v>43.16704253613885</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37903,28 +37903,28 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>334.2086062376757</v>
+        <v>335.2086062376757</v>
       </c>
       <c r="K42" t="n">
-        <v>400.1038546407913</v>
+        <v>401.1038546407913</v>
       </c>
       <c r="L42" t="n">
-        <v>411.26471692635</v>
+        <v>484.091375348687</v>
       </c>
       <c r="M42" t="n">
-        <v>295.9500421645043</v>
+        <v>296.9500421645043</v>
       </c>
       <c r="N42" t="n">
-        <v>343.6265501086548</v>
+        <v>344.6265501086548</v>
       </c>
       <c r="O42" t="n">
-        <v>450.4570219027464</v>
+        <v>451.4570219027464</v>
       </c>
       <c r="P42" t="n">
-        <v>322.6660045146532</v>
+        <v>256.2040133480641</v>
       </c>
       <c r="Q42" t="n">
-        <v>35.92073490952041</v>
+        <v>36.92073490952041</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -37979,7 +37979,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>32.36654437988173</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -38015,7 +38015,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>6.576933271976268</v>
+        <v>35.88256550003675</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -38061,25 +38061,25 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K44" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>356.8227662620851</v>
+        <v>311.0935791979517</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O44" t="n">
-        <v>774</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>774</v>
+        <v>772.0000000000067</v>
       </c>
       <c r="Q44" t="n">
         <v>443.0293889420883</v>
@@ -38140,25 +38140,25 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>293.2086062376757</v>
+        <v>289.2086062376757</v>
       </c>
       <c r="K45" t="n">
-        <v>359.1038546407913</v>
+        <v>355.1038546407913</v>
       </c>
       <c r="L45" t="n">
-        <v>306.9235339951383</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M45" t="n">
-        <v>254.9500421645043</v>
+        <v>195.0444078918343</v>
       </c>
       <c r="N45" t="n">
-        <v>302.6265501086548</v>
+        <v>298.6265501086548</v>
       </c>
       <c r="O45" t="n">
-        <v>409.4570219027464</v>
+        <v>405.4570219027464</v>
       </c>
       <c r="P45" t="n">
-        <v>281.6660045146532</v>
+        <v>277.6660045146532</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -38219,7 +38219,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>128.7310511640922</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -38252,7 +38252,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>10.37238299302163</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
